--- a/TUCUMAN 1061/Noviembre/tucuman Noviembre.xlsx
+++ b/TUCUMAN 1061/Noviembre/tucuman Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\TUCUMAN 1061\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\TUCUMAN 1061\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32992551-F71B-4ACF-9116-27179381B67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AA5DDF-44E2-4B66-9873-3C5BA7C5FFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilla" sheetId="2" r:id="rId1"/>
@@ -571,9 +571,6 @@
     <t>Honorarios - Inscripcion consorcio</t>
   </si>
   <si>
-    <t>Kromacolor compra RECUPLAS y Duralba - Muros</t>
-  </si>
-  <si>
     <t>Sr. Leonardo Balcazza trabajo en medianera (Altura)</t>
   </si>
   <si>
@@ -596,10 +593,13 @@
     <t>1 er vto</t>
   </si>
   <si>
-    <t>VTO: 14/11</t>
-  </si>
-  <si>
     <t>A JORGE EL MES PASADO LO PUSIMOS IMPAGO Y EL PAGO</t>
+  </si>
+  <si>
+    <t>VTO: 15/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Servisur visita y relevo de iluminacion </t>
   </si>
 </sst>
 </file>
@@ -1434,7 +1434,7 @@
     <xf numFmtId="167" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="265">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1733,189 +1733,6 @@
     <xf numFmtId="44" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="18" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="27" fillId="8" borderId="35" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="27" fillId="8" borderId="34" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="27" fillId="8" borderId="33" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="27" fillId="8" borderId="31" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="27" fillId="8" borderId="30" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="27" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="8" borderId="31" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="8" borderId="30" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
@@ -1932,6 +1749,191 @@
     <xf numFmtId="44" fontId="18" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="27" fillId="8" borderId="35" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="27" fillId="8" borderId="34" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="27" fillId="8" borderId="33" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="27" fillId="8" borderId="31" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="27" fillId="8" borderId="30" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="27" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="8" borderId="31" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="8" borderId="30" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="35" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="35" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2334,55 +2336,55 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" style="49" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" style="51" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="50" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" style="50" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="50" customWidth="1"/>
-    <col min="10" max="10" width="0.140625" style="50" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" style="50" customWidth="1"/>
-    <col min="12" max="12" width="0.140625" style="50" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" customWidth="1"/>
-    <col min="15" max="15" width="12.140625" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.44140625" style="49" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="51" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="50" customWidth="1"/>
+    <col min="8" max="8" width="7.5546875" style="50" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" style="50" customWidth="1"/>
+    <col min="10" max="10" width="0.109375" style="50" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" style="50" customWidth="1"/>
+    <col min="12" max="12" width="0.109375" style="50" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="12.109375" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.28515625" customWidth="1"/>
+    <col min="18" max="18" width="13.33203125" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
     <col min="20" max="20" width="12" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="193" t="str">
+    <row r="1" spans="1:22" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="205" t="str">
         <f>Gastos!E8</f>
         <v xml:space="preserve">PERIODO: OCTUBRE </v>
       </c>
-      <c r="B1" s="194"/>
-      <c r="C1" s="194"/>
-      <c r="D1" s="194"/>
-      <c r="E1" s="194"/>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="195"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
+      <c r="L1" s="206"/>
+      <c r="M1" s="206"/>
+      <c r="N1" s="206"/>
+      <c r="O1" s="206"/>
+      <c r="P1" s="206"/>
+      <c r="Q1" s="206"/>
+      <c r="R1" s="206"/>
+      <c r="S1" s="207"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="87"/>
       <c r="C2" s="177">
         <v>1554753.9300000002</v>
@@ -2393,17 +2395,17 @@
       <c r="J2" s="52"/>
       <c r="K2" s="52"/>
       <c r="L2" s="12"/>
-      <c r="M2" s="203" t="s">
-        <v>172</v>
-      </c>
-      <c r="N2" s="204"/>
-      <c r="O2" s="204"/>
-      <c r="P2" s="204"/>
-      <c r="Q2" s="204"/>
-      <c r="R2" s="204"/>
-      <c r="S2" s="205"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M2" s="215" t="s">
+        <v>171</v>
+      </c>
+      <c r="N2" s="216"/>
+      <c r="O2" s="216"/>
+      <c r="P2" s="216"/>
+      <c r="Q2" s="216"/>
+      <c r="R2" s="216"/>
+      <c r="S2" s="217"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="83"/>
       <c r="D3" s="177">
         <v>472904.04</v>
@@ -2413,56 +2415,56 @@
       <c r="I3" s="52"/>
       <c r="J3" s="52"/>
       <c r="L3" s="85"/>
-      <c r="M3" s="206"/>
-      <c r="N3" s="207"/>
-      <c r="O3" s="207"/>
-      <c r="P3" s="207"/>
-      <c r="Q3" s="207"/>
-      <c r="R3" s="207"/>
-      <c r="S3" s="208"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M3" s="218"/>
+      <c r="N3" s="219"/>
+      <c r="O3" s="219"/>
+      <c r="P3" s="219"/>
+      <c r="Q3" s="219"/>
+      <c r="R3" s="219"/>
+      <c r="S3" s="220"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="83"/>
-      <c r="C4" s="215" t="s">
+      <c r="C4" s="227" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="215"/>
+      <c r="D4" s="227"/>
       <c r="G4" s="52"/>
       <c r="H4" s="52"/>
       <c r="I4" s="52"/>
       <c r="J4" s="52"/>
       <c r="L4" s="85"/>
-      <c r="M4" s="206"/>
-      <c r="N4" s="207"/>
-      <c r="O4" s="207"/>
-      <c r="P4" s="207"/>
-      <c r="Q4" s="207"/>
-      <c r="R4" s="207"/>
-      <c r="S4" s="208"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M4" s="218"/>
+      <c r="N4" s="219"/>
+      <c r="O4" s="219"/>
+      <c r="P4" s="219"/>
+      <c r="Q4" s="219"/>
+      <c r="R4" s="219"/>
+      <c r="S4" s="220"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="83"/>
       <c r="B5" s="86"/>
-      <c r="C5" s="201">
+      <c r="C5" s="213">
         <f>D3</f>
         <v>472904.04</v>
       </c>
-      <c r="D5" s="201"/>
+      <c r="D5" s="213"/>
       <c r="E5" s="12"/>
       <c r="G5" s="52"/>
       <c r="H5" s="52"/>
       <c r="I5" s="52"/>
       <c r="J5" s="52"/>
       <c r="L5" s="85"/>
-      <c r="M5" s="206"/>
-      <c r="N5" s="207"/>
-      <c r="O5" s="207"/>
-      <c r="P5" s="207"/>
-      <c r="Q5" s="207"/>
-      <c r="R5" s="207"/>
-      <c r="S5" s="208"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M5" s="218"/>
+      <c r="N5" s="219"/>
+      <c r="O5" s="219"/>
+      <c r="P5" s="219"/>
+      <c r="Q5" s="219"/>
+      <c r="R5" s="219"/>
+      <c r="S5" s="220"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="83"/>
       <c r="C6" s="12" t="s">
         <v>156</v>
@@ -2475,22 +2477,22 @@
       <c r="J6" s="52"/>
       <c r="K6" s="52"/>
       <c r="L6" s="52"/>
-      <c r="M6" s="206"/>
-      <c r="N6" s="207"/>
-      <c r="O6" s="207"/>
-      <c r="P6" s="207"/>
-      <c r="Q6" s="207"/>
-      <c r="R6" s="207"/>
-      <c r="S6" s="208"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M6" s="218"/>
+      <c r="N6" s="219"/>
+      <c r="O6" s="219"/>
+      <c r="P6" s="219"/>
+      <c r="Q6" s="219"/>
+      <c r="R6" s="219"/>
+      <c r="S6" s="220"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="83"/>
       <c r="B7" s="82"/>
-      <c r="C7" s="201">
+      <c r="C7" s="213">
         <f>C2-D3</f>
         <v>1081849.8900000001</v>
       </c>
-      <c r="D7" s="201"/>
+      <c r="D7" s="213"/>
       <c r="E7" s="84"/>
       <c r="G7" s="52"/>
       <c r="H7" s="52"/>
@@ -2498,15 +2500,15 @@
       <c r="J7" s="52"/>
       <c r="K7" s="52"/>
       <c r="L7" s="52"/>
-      <c r="M7" s="206"/>
-      <c r="N7" s="207"/>
-      <c r="O7" s="207"/>
-      <c r="P7" s="207"/>
-      <c r="Q7" s="207"/>
-      <c r="R7" s="207"/>
-      <c r="S7" s="208"/>
-    </row>
-    <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M7" s="218"/>
+      <c r="N7" s="219"/>
+      <c r="O7" s="219"/>
+      <c r="P7" s="219"/>
+      <c r="Q7" s="219"/>
+      <c r="R7" s="219"/>
+      <c r="S7" s="220"/>
+    </row>
+    <row r="8" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="83"/>
       <c r="B8" s="82"/>
       <c r="C8" s="82" t="s">
@@ -2520,41 +2522,41 @@
       <c r="J8" s="52"/>
       <c r="K8" s="52"/>
       <c r="L8" s="52"/>
-      <c r="M8" s="206"/>
-      <c r="N8" s="207"/>
-      <c r="O8" s="207"/>
-      <c r="P8" s="207"/>
-      <c r="Q8" s="207"/>
-      <c r="R8" s="207"/>
-      <c r="S8" s="208"/>
-    </row>
-    <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="218"/>
+      <c r="N8" s="219"/>
+      <c r="O8" s="219"/>
+      <c r="P8" s="219"/>
+      <c r="Q8" s="219"/>
+      <c r="R8" s="219"/>
+      <c r="S8" s="220"/>
+    </row>
+    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="81"/>
       <c r="B9" s="80"/>
-      <c r="C9" s="202">
+      <c r="C9" s="214">
         <v>350000</v>
       </c>
-      <c r="D9" s="202"/>
+      <c r="D9" s="214"/>
       <c r="E9" s="79"/>
       <c r="F9" s="78"/>
-      <c r="G9" s="212" t="str">
+      <c r="G9" s="224" t="str">
         <f>Gastos!H8</f>
-        <v>VTO: 14/11</v>
-      </c>
-      <c r="H9" s="213"/>
-      <c r="I9" s="213"/>
-      <c r="J9" s="213"/>
-      <c r="K9" s="214"/>
+        <v>VTO: 15/12</v>
+      </c>
+      <c r="H9" s="225"/>
+      <c r="I9" s="225"/>
+      <c r="J9" s="225"/>
+      <c r="K9" s="226"/>
       <c r="L9" s="77"/>
-      <c r="M9" s="209"/>
-      <c r="N9" s="210"/>
-      <c r="O9" s="210"/>
-      <c r="P9" s="210"/>
-      <c r="Q9" s="210"/>
-      <c r="R9" s="210"/>
-      <c r="S9" s="211"/>
-    </row>
-    <row r="10" spans="1:22" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="221"/>
+      <c r="N9" s="222"/>
+      <c r="O9" s="222"/>
+      <c r="P9" s="222"/>
+      <c r="Q9" s="222"/>
+      <c r="R9" s="222"/>
+      <c r="S9" s="223"/>
+    </row>
+    <row r="10" spans="1:22" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="76" t="s">
         <v>32</v>
       </c>
@@ -2607,13 +2609,13 @@
         <v>25</v>
       </c>
       <c r="R10" s="72" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="S10" s="72" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="169" t="s">
         <v>80</v>
       </c>
@@ -2682,7 +2684,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="163" t="s">
         <v>81</v>
       </c>
@@ -2752,7 +2754,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="155" t="s">
         <v>82</v>
       </c>
@@ -2824,7 +2826,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="105" t="s">
         <v>83</v>
       </c>
@@ -2892,7 +2894,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="105" t="s">
         <v>84</v>
       </c>
@@ -2962,7 +2964,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="155" t="s">
         <v>85</v>
       </c>
@@ -2974,7 +2976,7 @@
         <v>158</v>
       </c>
       <c r="E16" s="158" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F16" s="159">
         <v>7.9</v>
@@ -3034,7 +3036,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="105" t="s">
         <v>86</v>
       </c>
@@ -3106,7 +3108,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="155" t="s">
         <v>87</v>
       </c>
@@ -3175,7 +3177,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="155" t="s">
         <v>88</v>
       </c>
@@ -3248,72 +3250,72 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="253" t="s">
+    <row r="20" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="192" t="s">
         <v>89</v>
       </c>
       <c r="B20" s="152"/>
-      <c r="C20" s="254" t="s">
+      <c r="C20" s="193" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="255" t="s">
+      <c r="D20" s="194" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="256"/>
-      <c r="F20" s="257">
+      <c r="E20" s="195"/>
+      <c r="F20" s="196">
         <v>7.9</v>
       </c>
-      <c r="G20" s="258">
+      <c r="G20" s="197">
         <v>152965.07008999999</v>
       </c>
-      <c r="H20" s="259"/>
-      <c r="I20" s="258"/>
-      <c r="J20" s="259"/>
-      <c r="K20" s="259">
+      <c r="H20" s="198"/>
+      <c r="I20" s="197"/>
+      <c r="J20" s="198"/>
+      <c r="K20" s="198">
         <f t="shared" si="10"/>
         <v>152965.07008999999</v>
       </c>
-      <c r="L20" s="259"/>
-      <c r="M20" s="260">
+      <c r="L20" s="198"/>
+      <c r="M20" s="199">
         <f t="shared" si="3"/>
         <v>4588.9521027000001</v>
       </c>
-      <c r="N20" s="260">
+      <c r="N20" s="199">
         <f t="shared" ref="N20:N29" si="11">K20+M20+L20</f>
         <v>157554.02219269998</v>
       </c>
-      <c r="O20" s="259">
+      <c r="O20" s="198">
         <f t="shared" si="4"/>
         <v>85466.141310000006</v>
       </c>
-      <c r="P20" s="258">
+      <c r="P20" s="197">
         <f t="shared" si="5"/>
         <v>27650</v>
       </c>
-      <c r="Q20" s="258">
+      <c r="Q20" s="197">
         <f t="shared" si="6"/>
         <v>37359.419160000005</v>
       </c>
-      <c r="R20" s="261">
+      <c r="R20" s="200">
         <f t="shared" si="7"/>
         <v>308030.09999999998</v>
       </c>
-      <c r="S20" s="262">
+      <c r="S20" s="201">
         <f t="shared" si="8"/>
         <v>317271.09999999998</v>
       </c>
-      <c r="T20" s="263">
+      <c r="T20" s="202">
         <f t="shared" si="9"/>
         <v>9.9999999999999992E-2</v>
       </c>
-      <c r="U20" s="264" t="s">
-        <v>175</v>
+      <c r="U20" s="203" t="s">
+        <v>173</v>
       </c>
       <c r="V20" s="89" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="155" t="s">
         <v>90</v>
       </c>
@@ -3377,7 +3379,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="155" t="s">
         <v>91</v>
       </c>
@@ -3441,7 +3443,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="105"/>
       <c r="B23" s="67"/>
       <c r="C23" s="89" t="s">
@@ -3504,7 +3506,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="155"/>
       <c r="B24" s="156"/>
       <c r="C24" s="90" t="s">
@@ -3567,7 +3569,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="105"/>
       <c r="B25" s="67"/>
       <c r="C25" s="89" t="s">
@@ -3628,7 +3630,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="155"/>
       <c r="B26" s="152"/>
       <c r="C26" s="90" t="s">
@@ -3696,7 +3698,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="105"/>
       <c r="B27" s="67"/>
       <c r="C27" s="89" t="s">
@@ -3765,7 +3767,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="178"/>
       <c r="B28" s="179"/>
       <c r="C28" s="90" t="s">
@@ -3776,7 +3778,7 @@
         <v>Perez Sebastian</v>
       </c>
       <c r="E28" s="158" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F28" s="180">
         <v>0.74</v>
@@ -3835,7 +3837,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:22" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="155"/>
       <c r="B29" s="168"/>
       <c r="C29" s="90" t="s">
@@ -3903,7 +3905,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="69"/>
       <c r="B30" s="67"/>
       <c r="C30" s="66"/>
@@ -3932,10 +3934,10 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:22" s="54" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="199"/>
-      <c r="B31" s="200"/>
-      <c r="C31" s="200"/>
+    <row r="31" spans="1:22" s="54" customFormat="1" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="211"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="212"/>
       <c r="D31" s="59"/>
       <c r="E31" s="59"/>
       <c r="F31" s="92"/>
@@ -3983,32 +3985,32 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="196" t="s">
+    <row r="32" spans="1:22" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="208" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="197"/>
-      <c r="D32" s="197"/>
-      <c r="E32" s="197"/>
-      <c r="F32" s="197"/>
-      <c r="G32" s="197"/>
-      <c r="H32" s="197"/>
-      <c r="I32" s="197"/>
-      <c r="J32" s="197"/>
-      <c r="K32" s="197"/>
-      <c r="L32" s="197"/>
-      <c r="M32" s="197"/>
-      <c r="N32" s="197"/>
-      <c r="O32" s="197"/>
-      <c r="P32" s="197"/>
-      <c r="Q32" s="197"/>
-      <c r="R32" s="197"/>
-      <c r="S32" s="198"/>
+      <c r="C32" s="209"/>
+      <c r="D32" s="209"/>
+      <c r="E32" s="209"/>
+      <c r="F32" s="209"/>
+      <c r="G32" s="209"/>
+      <c r="H32" s="209"/>
+      <c r="I32" s="209"/>
+      <c r="J32" s="209"/>
+      <c r="K32" s="209"/>
+      <c r="L32" s="209"/>
+      <c r="M32" s="209"/>
+      <c r="N32" s="209"/>
+      <c r="O32" s="209"/>
+      <c r="P32" s="209"/>
+      <c r="Q32" s="209"/>
+      <c r="R32" s="209"/>
+      <c r="S32" s="210"/>
       <c r="V32" s="89" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="3:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:22" x14ac:dyDescent="0.3">
       <c r="F33" s="53"/>
       <c r="G33" s="52"/>
       <c r="H33" s="52"/>
@@ -4022,80 +4024,80 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C34" s="192"/>
-      <c r="D34" s="192"/>
-      <c r="E34" s="192"/>
-      <c r="F34" s="192"/>
-      <c r="G34" s="192"/>
-      <c r="H34" s="192"/>
-      <c r="I34" s="192"/>
-      <c r="J34" s="192"/>
-      <c r="K34" s="192"/>
-      <c r="L34" s="192"/>
-      <c r="M34" s="192"/>
-      <c r="N34" s="192"/>
-      <c r="O34" s="192"/>
-    </row>
-    <row r="35" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C35" s="192"/>
-      <c r="D35" s="192"/>
-      <c r="E35" s="192"/>
-      <c r="F35" s="192"/>
-      <c r="G35" s="192"/>
-      <c r="H35" s="192"/>
-      <c r="I35" s="192"/>
-      <c r="J35" s="192"/>
-      <c r="K35" s="192"/>
-      <c r="L35" s="192"/>
-      <c r="M35" s="192"/>
-      <c r="N35" s="192"/>
-      <c r="O35" s="192"/>
-    </row>
-    <row r="36" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C36" s="192"/>
-      <c r="D36" s="192"/>
-      <c r="E36" s="192"/>
-      <c r="F36" s="192"/>
-      <c r="G36" s="192"/>
-      <c r="H36" s="192"/>
-      <c r="I36" s="192"/>
-      <c r="J36" s="192"/>
-      <c r="K36" s="192"/>
-      <c r="L36" s="192"/>
-      <c r="M36" s="192"/>
-      <c r="N36" s="192"/>
-      <c r="O36" s="192"/>
-    </row>
-    <row r="37" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C37" s="192"/>
-      <c r="D37" s="192"/>
-      <c r="E37" s="192"/>
-      <c r="F37" s="192"/>
-      <c r="G37" s="192"/>
-      <c r="H37" s="192"/>
-      <c r="I37" s="192"/>
-      <c r="J37" s="192"/>
-      <c r="K37" s="192"/>
-      <c r="L37" s="192"/>
-      <c r="M37" s="192"/>
-      <c r="N37" s="192"/>
-      <c r="O37" s="192"/>
-    </row>
-    <row r="38" spans="3:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="192"/>
-      <c r="D38" s="192"/>
-      <c r="E38" s="192"/>
-      <c r="F38" s="192"/>
-      <c r="G38" s="192"/>
-      <c r="H38" s="192"/>
-      <c r="I38" s="192"/>
-      <c r="J38" s="192"/>
-      <c r="K38" s="192"/>
-      <c r="L38" s="192"/>
-      <c r="M38" s="192"/>
-      <c r="N38" s="192"/>
-      <c r="O38" s="192"/>
+    <row r="34" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C34" s="204"/>
+      <c r="D34" s="204"/>
+      <c r="E34" s="204"/>
+      <c r="F34" s="204"/>
+      <c r="G34" s="204"/>
+      <c r="H34" s="204"/>
+      <c r="I34" s="204"/>
+      <c r="J34" s="204"/>
+      <c r="K34" s="204"/>
+      <c r="L34" s="204"/>
+      <c r="M34" s="204"/>
+      <c r="N34" s="204"/>
+      <c r="O34" s="204"/>
+    </row>
+    <row r="35" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C35" s="204"/>
+      <c r="D35" s="204"/>
+      <c r="E35" s="204"/>
+      <c r="F35" s="204"/>
+      <c r="G35" s="204"/>
+      <c r="H35" s="204"/>
+      <c r="I35" s="204"/>
+      <c r="J35" s="204"/>
+      <c r="K35" s="204"/>
+      <c r="L35" s="204"/>
+      <c r="M35" s="204"/>
+      <c r="N35" s="204"/>
+      <c r="O35" s="204"/>
+    </row>
+    <row r="36" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C36" s="204"/>
+      <c r="D36" s="204"/>
+      <c r="E36" s="204"/>
+      <c r="F36" s="204"/>
+      <c r="G36" s="204"/>
+      <c r="H36" s="204"/>
+      <c r="I36" s="204"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="204"/>
+      <c r="L36" s="204"/>
+      <c r="M36" s="204"/>
+      <c r="N36" s="204"/>
+      <c r="O36" s="204"/>
+    </row>
+    <row r="37" spans="3:22" x14ac:dyDescent="0.3">
+      <c r="C37" s="204"/>
+      <c r="D37" s="204"/>
+      <c r="E37" s="204"/>
+      <c r="F37" s="204"/>
+      <c r="G37" s="204"/>
+      <c r="H37" s="204"/>
+      <c r="I37" s="204"/>
+      <c r="J37" s="204"/>
+      <c r="K37" s="204"/>
+      <c r="L37" s="204"/>
+      <c r="M37" s="204"/>
+      <c r="N37" s="204"/>
+      <c r="O37" s="204"/>
+    </row>
+    <row r="38" spans="3:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="204"/>
+      <c r="D38" s="204"/>
+      <c r="E38" s="204"/>
+      <c r="F38" s="204"/>
+      <c r="G38" s="204"/>
+      <c r="H38" s="204"/>
+      <c r="I38" s="204"/>
+      <c r="J38" s="204"/>
+      <c r="K38" s="204"/>
+      <c r="L38" s="204"/>
+      <c r="M38" s="204"/>
+      <c r="N38" s="204"/>
+      <c r="O38" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4119,14 +4121,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4139,18 +4141,18 @@
       <c r="G1" s="1"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="D2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="216">
+      <c r="E2" s="228">
         <v>1153202676</v>
       </c>
-      <c r="F2" s="216"/>
+      <c r="F2" s="228"/>
       <c r="H2" s="6"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="D3" s="12" t="s">
         <v>2</v>
@@ -4160,7 +4162,7 @@
       </c>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="D4" t="s">
         <v>17</v>
@@ -4168,33 +4170,33 @@
       <c r="H4" s="6"/>
       <c r="J4" s="186"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
-      <c r="D5" s="217" t="s">
+      <c r="D5" s="229" t="s">
         <v>160</v>
       </c>
-      <c r="E5" s="217"/>
-      <c r="F5" s="217"/>
-      <c r="G5" s="217"/>
-      <c r="H5" s="218"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E5" s="229"/>
+      <c r="F5" s="229"/>
+      <c r="G5" s="229"/>
+      <c r="H5" s="230"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-      <c r="D6" s="217"/>
-      <c r="E6" s="217"/>
-      <c r="F6" s="217"/>
-      <c r="G6" s="217"/>
-      <c r="H6" s="218"/>
-    </row>
-    <row r="7" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="229"/>
+      <c r="E6" s="229"/>
+      <c r="F6" s="229"/>
+      <c r="G6" s="229"/>
+      <c r="H6" s="230"/>
+    </row>
+    <row r="7" spans="1:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="D7" s="217"/>
-      <c r="E7" s="217"/>
-      <c r="F7" s="217"/>
-      <c r="G7" s="217"/>
-      <c r="H7" s="218"/>
-    </row>
-    <row r="8" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D7" s="229"/>
+      <c r="E7" s="229"/>
+      <c r="F7" s="229"/>
+      <c r="G7" s="229"/>
+      <c r="H7" s="230"/>
+    </row>
+    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>3</v>
       </c>
@@ -4210,7 +4212,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -4220,11 +4222,11 @@
       <c r="G9" s="1"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>4</v>
       </c>
@@ -4233,7 +4235,7 @@
       </c>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -4243,19 +4245,19 @@
       <c r="G12" s="2"/>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="230" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="242" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="230"/>
-      <c r="C13" s="230"/>
-      <c r="D13" s="230"/>
-      <c r="E13" s="230"/>
-      <c r="F13" s="230"/>
-      <c r="G13" s="230"/>
-      <c r="H13" s="230"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="242"/>
+      <c r="C13" s="242"/>
+      <c r="D13" s="242"/>
+      <c r="E13" s="242"/>
+      <c r="F13" s="242"/>
+      <c r="G13" s="242"/>
+      <c r="H13" s="242"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="17"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -4265,7 +4267,7 @@
       <c r="G14" s="18"/>
       <c r="H14" s="187"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
         <v>60</v>
       </c>
@@ -4282,7 +4284,7 @@
         <v>400115.4</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="93" t="s">
         <v>162</v>
       </c>
@@ -4292,11 +4294,11 @@
       <c r="E16" s="18"/>
       <c r="F16" s="18"/>
       <c r="G16" s="18"/>
-      <c r="H16" s="183">
+      <c r="H16" s="265">
         <v>4030.28</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>5</v>
       </c>
@@ -4311,7 +4313,7 @@
         <v>404145.68000000005</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="21"/>
       <c r="B18" s="22"/>
       <c r="C18" s="22"/>
@@ -4321,19 +4323,19 @@
       <c r="G18" s="22"/>
       <c r="H18" s="39"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="231" t="s">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="243" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="232"/>
-      <c r="C19" s="232"/>
-      <c r="D19" s="232"/>
-      <c r="E19" s="232"/>
-      <c r="F19" s="232"/>
-      <c r="G19" s="232"/>
-      <c r="H19" s="233"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="244"/>
+      <c r="C19" s="244"/>
+      <c r="D19" s="244"/>
+      <c r="E19" s="244"/>
+      <c r="F19" s="244"/>
+      <c r="G19" s="244"/>
+      <c r="H19" s="245"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>59</v>
       </c>
@@ -4343,12 +4345,11 @@
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="24">
-        <f>17878.5*2</f>
-        <v>35757</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H20" s="266">
+        <v>17336.11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
         <v>58</v>
       </c>
@@ -4362,7 +4363,7 @@
         <v>472904.04</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>7</v>
       </c>
@@ -4374,23 +4375,23 @@
       <c r="G22" s="20"/>
       <c r="H22" s="25">
         <f>SUM(H20:H21)</f>
-        <v>508661.04</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="234" t="s">
+        <v>490240.14999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="246" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="234"/>
-      <c r="C23" s="234"/>
-      <c r="D23" s="234"/>
-      <c r="E23" s="234"/>
-      <c r="F23" s="234"/>
-      <c r="G23" s="234"/>
-      <c r="H23" s="234"/>
+      <c r="B23" s="246"/>
+      <c r="C23" s="246"/>
+      <c r="D23" s="246"/>
+      <c r="E23" s="246"/>
+      <c r="F23" s="246"/>
+      <c r="G23" s="246"/>
+      <c r="H23" s="246"/>
       <c r="J23" s="24"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="93" t="s">
         <v>141</v>
       </c>
@@ -4400,13 +4401,13 @@
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
       <c r="G24" s="18"/>
-      <c r="H24" s="24">
+      <c r="H24" s="266">
         <v>46638</v>
       </c>
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="93" t="s">
         <v>164</v>
       </c>
@@ -4422,9 +4423,9 @@
       <c r="I25" s="13"/>
       <c r="J25" s="13"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="93" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B26" s="18"/>
       <c r="C26" s="23"/>
@@ -4432,13 +4433,13 @@
       <c r="E26" s="18"/>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
-      <c r="H26" s="24">
-        <v>224969.09</v>
+      <c r="H26" s="266">
+        <v>20000</v>
       </c>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
     </row>
-    <row r="27" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="93" t="s">
         <v>143</v>
       </c>
@@ -4448,11 +4449,11 @@
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
-      <c r="H27" s="24">
+      <c r="H27" s="266">
         <v>75000</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>8</v>
       </c>
@@ -4464,22 +4465,22 @@
       <c r="G28" s="20"/>
       <c r="H28" s="25">
         <f>SUM(H24:H27)</f>
-        <v>373207.08999999997</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="231" t="s">
+        <v>168238</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="243" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="232"/>
-      <c r="C29" s="232"/>
-      <c r="D29" s="232"/>
-      <c r="E29" s="232"/>
-      <c r="F29" s="232"/>
-      <c r="G29" s="232"/>
-      <c r="H29" s="233"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="244"/>
+      <c r="C29" s="244"/>
+      <c r="D29" s="244"/>
+      <c r="E29" s="244"/>
+      <c r="F29" s="244"/>
+      <c r="G29" s="244"/>
+      <c r="H29" s="245"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
         <v>9</v>
       </c>
@@ -4496,7 +4497,7 @@
       </c>
       <c r="I30" s="40"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="17" t="s">
         <v>166</v>
       </c>
@@ -4511,7 +4512,7 @@
       </c>
       <c r="I31" s="40"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="17" t="s">
         <v>165</v>
       </c>
@@ -4526,7 +4527,7 @@
       </c>
       <c r="I32" s="40"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
         <v>163</v>
       </c>
@@ -4545,7 +4546,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="17"/>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
@@ -4555,21 +4556,21 @@
       <c r="G34" s="18"/>
       <c r="H34" s="26"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="231" t="s">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="243" t="s">
+        <v>168</v>
+      </c>
+      <c r="B35" s="244"/>
+      <c r="C35" s="244"/>
+      <c r="D35" s="244"/>
+      <c r="E35" s="244"/>
+      <c r="F35" s="244"/>
+      <c r="G35" s="244"/>
+      <c r="H35" s="245"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="46" t="s">
         <v>169</v>
-      </c>
-      <c r="B35" s="232"/>
-      <c r="C35" s="232"/>
-      <c r="D35" s="232"/>
-      <c r="E35" s="232"/>
-      <c r="F35" s="232"/>
-      <c r="G35" s="232"/>
-      <c r="H35" s="233"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="46" t="s">
-        <v>170</v>
       </c>
       <c r="B36" s="47"/>
       <c r="C36" s="47"/>
@@ -4582,7 +4583,7 @@
       </c>
       <c r="J36" s="14"/>
     </row>
-    <row r="37" spans="1:14" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" s="15" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="27" t="s">
         <v>15</v>
       </c>
@@ -4594,10 +4595,10 @@
       <c r="G37" s="28"/>
       <c r="H37" s="29">
         <f>H17+H22+H28+H33+H36</f>
-        <v>1554753.9300000002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" s="13" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+        <v>1331363.9500000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A38" s="42" t="s">
         <v>150</v>
       </c>
@@ -4609,70 +4610,70 @@
       <c r="G38" s="43"/>
       <c r="H38" s="44"/>
     </row>
-    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="221" t="s">
+    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="233" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="222"/>
-      <c r="C39" s="222"/>
-      <c r="D39" s="222"/>
-      <c r="E39" s="222"/>
-      <c r="F39" s="222"/>
-      <c r="G39" s="222"/>
-      <c r="H39" s="223"/>
+      <c r="B39" s="234"/>
+      <c r="C39" s="234"/>
+      <c r="D39" s="234"/>
+      <c r="E39" s="234"/>
+      <c r="F39" s="234"/>
+      <c r="G39" s="234"/>
+      <c r="H39" s="235"/>
       <c r="I39" s="162"/>
       <c r="K39" s="162"/>
     </row>
-    <row r="40" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="224"/>
-      <c r="B40" s="225"/>
-      <c r="C40" s="225"/>
-      <c r="D40" s="225"/>
-      <c r="E40" s="225"/>
-      <c r="F40" s="225"/>
-      <c r="G40" s="225"/>
-      <c r="H40" s="226"/>
-    </row>
-    <row r="41" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="241" t="s">
-        <v>168</v>
-      </c>
-      <c r="B41" s="242"/>
-      <c r="C41" s="242"/>
-      <c r="D41" s="242"/>
-      <c r="E41" s="242"/>
-      <c r="F41" s="242"/>
-      <c r="G41" s="243"/>
+    <row r="40" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="236"/>
+      <c r="B40" s="237"/>
+      <c r="C40" s="237"/>
+      <c r="D40" s="237"/>
+      <c r="E40" s="237"/>
+      <c r="F40" s="237"/>
+      <c r="G40" s="237"/>
+      <c r="H40" s="238"/>
+    </row>
+    <row r="41" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="253" t="s">
+        <v>167</v>
+      </c>
+      <c r="B41" s="254"/>
+      <c r="C41" s="254"/>
+      <c r="D41" s="254"/>
+      <c r="E41" s="254"/>
+      <c r="F41" s="254"/>
+      <c r="G41" s="255"/>
       <c r="H41" s="185">
         <v>350000</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="235"/>
-      <c r="B42" s="236"/>
-      <c r="C42" s="236"/>
-      <c r="D42" s="236"/>
-      <c r="E42" s="236"/>
-      <c r="F42" s="236"/>
-      <c r="G42" s="237"/>
+    <row r="42" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="247"/>
+      <c r="B42" s="248"/>
+      <c r="C42" s="248"/>
+      <c r="D42" s="248"/>
+      <c r="E42" s="248"/>
+      <c r="F42" s="248"/>
+      <c r="G42" s="249"/>
       <c r="H42" s="30"/>
     </row>
-    <row r="43" spans="1:14" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="238" t="s">
+    <row r="43" spans="1:14" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="250" t="s">
         <v>16</v>
       </c>
-      <c r="B43" s="239"/>
-      <c r="C43" s="239"/>
-      <c r="D43" s="239"/>
-      <c r="E43" s="239"/>
-      <c r="F43" s="239"/>
-      <c r="G43" s="240"/>
+      <c r="B43" s="251"/>
+      <c r="C43" s="251"/>
+      <c r="D43" s="251"/>
+      <c r="E43" s="251"/>
+      <c r="F43" s="251"/>
+      <c r="G43" s="252"/>
       <c r="H43" s="31">
         <f>SUM(H41:H42)</f>
         <v>350000</v>
       </c>
     </row>
-    <row r="44" spans="1:14" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="181"/>
       <c r="B44" s="181"/>
       <c r="C44" s="181"/>
@@ -4682,27 +4683,27 @@
       <c r="G44" s="181"/>
       <c r="H44" s="182"/>
     </row>
-    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H45" s="18"/>
       <c r="J45" s="14"/>
     </row>
-    <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="219" t="s">
+    <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="231" t="s">
         <v>144</v>
       </c>
-      <c r="B46" s="219"/>
-      <c r="C46" s="219"/>
-      <c r="D46" s="219"/>
-      <c r="E46" s="219"/>
-      <c r="F46" s="219"/>
-      <c r="G46" s="219"/>
+      <c r="B46" s="231"/>
+      <c r="C46" s="231"/>
+      <c r="D46" s="231"/>
+      <c r="E46" s="231"/>
+      <c r="F46" s="231"/>
+      <c r="G46" s="231"/>
       <c r="H46" s="29">
         <f>+H37+H38</f>
-        <v>1554753.9300000002</v>
+        <v>1331363.9500000002</v>
       </c>
       <c r="J46" s="162"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="18"/>
       <c r="B47" s="18"/>
       <c r="C47" s="18"/>
@@ -4712,7 +4713,7 @@
       <c r="G47" s="18"/>
       <c r="H47" s="18"/>
     </row>
-    <row r="48" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="27" t="s">
         <v>154</v>
       </c>
@@ -4727,7 +4728,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="18"/>
       <c r="B49" s="18"/>
       <c r="C49" s="18"/>
@@ -4737,33 +4738,33 @@
       <c r="G49" s="18"/>
       <c r="H49" s="18"/>
     </row>
-    <row r="50" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="227" t="s">
+    <row r="50" spans="1:10" ht="18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="239" t="s">
         <v>13</v>
       </c>
-      <c r="B50" s="228"/>
-      <c r="C50" s="228"/>
-      <c r="D50" s="228"/>
-      <c r="E50" s="228"/>
-      <c r="F50" s="228"/>
-      <c r="G50" s="228"/>
-      <c r="H50" s="229"/>
-    </row>
-    <row r="51" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="220" t="s">
+      <c r="B50" s="240"/>
+      <c r="C50" s="240"/>
+      <c r="D50" s="240"/>
+      <c r="E50" s="240"/>
+      <c r="F50" s="240"/>
+      <c r="G50" s="240"/>
+      <c r="H50" s="241"/>
+    </row>
+    <row r="51" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="232" t="s">
         <v>151</v>
       </c>
-      <c r="B51" s="220"/>
-      <c r="C51" s="220"/>
-      <c r="D51" s="220"/>
-      <c r="E51" s="220"/>
-      <c r="F51" s="220"/>
-      <c r="G51" s="220"/>
+      <c r="B51" s="232"/>
+      <c r="C51" s="232"/>
+      <c r="D51" s="232"/>
+      <c r="E51" s="232"/>
+      <c r="F51" s="232"/>
+      <c r="G51" s="232"/>
       <c r="H51" s="38">
         <v>2287941.4208707316</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="33" t="s">
         <v>148</v>
       </c>
@@ -4778,7 +4779,7 @@
         <v>1244480.3504500003</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="33" t="s">
         <v>149</v>
       </c>
@@ -4790,11 +4791,11 @@
       <c r="G53" s="34"/>
       <c r="H53" s="35">
         <f>-(H37+H43)</f>
-        <v>-1904753.9300000002</v>
+        <v>-1681363.9500000002</v>
       </c>
       <c r="J53" s="14"/>
     </row>
-    <row r="54" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A54" s="36" t="s">
         <v>14</v>
       </c>
@@ -4806,7 +4807,7 @@
       <c r="G54" s="37"/>
       <c r="H54" s="45">
         <f>SUM(H51:H53)</f>
-        <v>1627667.8413207317</v>
+        <v>1851057.8213207317</v>
       </c>
     </row>
   </sheetData>
@@ -4835,31 +4836,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="109" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="109" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" style="109" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="109" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="109" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.42578125" style="109" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="109" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="109" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="109" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" style="109" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="109" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.44140625" style="109" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="109" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.42578125" style="109"/>
-    <col min="13" max="13" width="14.7109375" style="109" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5703125" style="109" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="109"/>
+    <col min="9" max="12" width="11.44140625" style="109"/>
+    <col min="13" max="13" width="14.6640625" style="109" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5546875" style="109" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.44140625" style="109"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="244" t="s">
+    <row r="1" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="256" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="245"/>
-      <c r="C1" s="245"/>
-      <c r="D1" s="245"/>
-      <c r="E1" s="246"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B1" s="257"/>
+      <c r="C1" s="257"/>
+      <c r="D1" s="257"/>
+      <c r="E1" s="258"/>
+    </row>
+    <row r="2" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="150"/>
       <c r="B2" s="135"/>
       <c r="C2" s="135"/>
@@ -4868,7 +4869,7 @@
       </c>
       <c r="E2" s="146"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="148">
         <f>13+28+19</f>
         <v>60</v>
@@ -4890,38 +4891,38 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="145"/>
       <c r="B4" s="144"/>
       <c r="C4" s="144"/>
       <c r="D4" s="144"/>
       <c r="E4" s="143"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="142"/>
       <c r="B5" s="142"/>
       <c r="C5" s="142"/>
       <c r="D5" s="142"/>
       <c r="E5" s="142"/>
     </row>
-    <row r="6" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="142"/>
       <c r="B6" s="142"/>
       <c r="C6" s="142"/>
       <c r="D6" s="142"/>
       <c r="E6" s="142"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="247" t="s">
+    <row r="7" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="259" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="248"/>
-      <c r="C7" s="248"/>
-      <c r="D7" s="248"/>
-      <c r="E7" s="248"/>
-      <c r="F7" s="248"/>
-      <c r="G7" s="248"/>
-      <c r="H7" s="249"/>
+      <c r="B7" s="260"/>
+      <c r="C7" s="260"/>
+      <c r="D7" s="260"/>
+      <c r="E7" s="260"/>
+      <c r="F7" s="260"/>
+      <c r="G7" s="260"/>
+      <c r="H7" s="261"/>
       <c r="L7" s="109" t="s">
         <v>71</v>
       </c>
@@ -4929,7 +4930,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="102">
         <v>400523.88</v>
       </c>
@@ -4965,7 +4966,7 @@
         <v>2365.2600000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="138" t="s">
         <v>34</v>
       </c>
@@ -5014,7 +5015,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="136" t="s">
         <v>35</v>
       </c>
@@ -5063,7 +5064,7 @@
         <v>6.4240000000000005E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="136" t="s">
         <v>36</v>
       </c>
@@ -5111,7 +5112,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="136" t="s">
         <v>37</v>
       </c>
@@ -5158,7 +5159,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="136" t="s">
         <v>38</v>
       </c>
@@ -5201,7 +5202,7 @@
         <v>3266.9389024000006</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="136" t="s">
         <v>39</v>
       </c>
@@ -5236,7 +5237,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="136" t="s">
         <v>40</v>
       </c>
@@ -5275,7 +5276,7 @@
         <v>13227.0974549</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="136" t="s">
         <v>41</v>
       </c>
@@ -5310,7 +5311,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="136" t="s">
         <v>42</v>
       </c>
@@ -5345,7 +5346,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="136" t="s">
         <v>43</v>
       </c>
@@ -5380,7 +5381,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="136" t="s">
         <v>44</v>
       </c>
@@ -5415,7 +5416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="136" t="s">
         <v>45</v>
       </c>
@@ -5447,7 +5448,7 @@
         <v>37634.994823379922</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="134" t="s">
         <v>138</v>
       </c>
@@ -5469,7 +5470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="95">
         <f>+D21/E8</f>
         <v>0.70190597204574334</v>
@@ -5479,7 +5480,7 @@
       </c>
       <c r="L22" s="129"/>
     </row>
-    <row r="23" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="94">
         <f>100%-A22</f>
         <v>0.29809402795425666</v>
@@ -5488,35 +5489,35 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="127"/>
       <c r="J25" s="109">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="J26" s="109">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J27" s="109">
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B28" s="250" t="s">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B28" s="262" t="s">
         <v>137</v>
       </c>
-      <c r="C28" s="251"/>
-      <c r="D28" s="251"/>
-      <c r="E28" s="251"/>
-      <c r="F28" s="252"/>
+      <c r="C28" s="263"/>
+      <c r="D28" s="263"/>
+      <c r="E28" s="263"/>
+      <c r="F28" s="264"/>
       <c r="J28" s="109">
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B29" s="126" t="s">
         <v>136</v>
       </c>
@@ -5536,7 +5537,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B30" s="120" t="s">
         <v>131</v>
       </c>
@@ -5559,7 +5560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B31" s="120" t="s">
         <v>130</v>
       </c>
@@ -5578,7 +5579,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B32" s="120" t="s">
         <v>129</v>
       </c>
@@ -5597,7 +5598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B33" s="120" t="s">
         <v>128</v>
       </c>
@@ -5620,7 +5621,7 @@
         <v>0.31000000000130967</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B34" s="120" t="s">
         <v>127</v>
       </c>
@@ -5639,7 +5640,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B35" s="120" t="s">
         <v>126</v>
       </c>
@@ -5658,7 +5659,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B36" s="120" t="s">
         <v>125</v>
       </c>
@@ -5677,7 +5678,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B37" s="120" t="s">
         <v>124</v>
       </c>
@@ -5693,7 +5694,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B38" s="120" t="s">
         <v>123</v>
       </c>
@@ -5715,7 +5716,7 @@
         <v>-11.950000000000003</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B39" s="120" t="s">
         <v>121</v>
       </c>
@@ -5729,7 +5730,7 @@
         <v>36500</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B40" s="120" t="s">
         <v>120</v>
       </c>
@@ -5743,7 +5744,7 @@
         <v>40500</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B41" s="120" t="s">
         <v>119</v>
       </c>
@@ -5757,7 +5758,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="42" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B42" s="120" t="s">
         <v>118</v>
       </c>
@@ -5771,7 +5772,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B43" s="120" t="s">
         <v>117</v>
       </c>
@@ -5785,7 +5786,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="44" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B44" s="117" t="s">
         <v>116</v>
       </c>
@@ -5799,7 +5800,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B45" s="117" t="s">
         <v>115</v>
       </c>
@@ -5813,7 +5814,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B46" s="117" t="s">
         <v>114</v>
       </c>
@@ -5827,7 +5828,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="113" t="s">
         <v>113</v>
       </c>

--- a/TUCUMAN 1061/Noviembre/tucuman Noviembre.xlsx
+++ b/TUCUMAN 1061/Noviembre/tucuman Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\TUCUMAN 1061\Noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\TUCUMAN 1061\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8B307F-7455-4C06-BDDD-D5CA711014C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8FC884-D97F-4A00-A2CC-67E3125B1016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gastos" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="166">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -201,39 +201,6 @@
   </si>
   <si>
     <t>6to. "B"</t>
-  </si>
-  <si>
-    <t>7mo. "A"</t>
-  </si>
-  <si>
-    <t>7mo. "B"</t>
-  </si>
-  <si>
-    <t>8vo. "A"</t>
-  </si>
-  <si>
-    <t>8vo. "B"</t>
-  </si>
-  <si>
-    <t>9no. "A"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COCHERA 1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">COCHERA 2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">COCHERA 7 </t>
-  </si>
-  <si>
-    <t>COCHERA 8</t>
-  </si>
-  <si>
-    <t>COCHERA 9</t>
-  </si>
-  <si>
-    <t>COCHERA 10</t>
   </si>
   <si>
     <t>ROSALES 624</t>
@@ -600,6 +567,9 @@
   </si>
   <si>
     <t>SOLICITAMOS POR FAVOR QUE, SI REALIZAN EL PAGO ANTES DE LA FECHA DEL PRIMER VENCIMIENTO (EN ESTE CASO, EL 15/12), ABONEN ÚNICAMENTE EL MONTO CORRESPONDIENTE A DICHO VENCIMIENTO Y NO EL DEL SEGUNDO.</t>
+  </si>
+  <si>
+    <t>la habiamos puesto impaga</t>
   </si>
 </sst>
 </file>
@@ -1418,7 +1388,7 @@
     <xf numFmtId="167" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="291">
+  <cellXfs count="293">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1525,7 +1495,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1674,151 +1643,15 @@
     <xf numFmtId="44" fontId="18" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="17" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="8" borderId="35" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="8" borderId="34" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="8" borderId="33" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="8" borderId="31" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="8" borderId="30" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="26" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="25" fillId="8" borderId="31" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="25" fillId="8" borderId="30" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="25" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="34" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -1832,12 +1665,11 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="21" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="17" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="17" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="18" fillId="9" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="9" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="18" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1847,90 +1679,22 @@
     <xf numFmtId="2" fontId="17" fillId="9" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="36" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="11" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="11" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="11" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="37" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="6" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1944,6 +1708,24 @@
     <xf numFmtId="8" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="6" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1962,18 +1744,210 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="36" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="11" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="11" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="11" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="8" borderId="35" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="8" borderId="34" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="8" borderId="33" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="8" borderId="31" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="8" borderId="30" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="26" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="8" borderId="31" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="8" borderId="30" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2318,14 +2292,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:N55"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2333,67 +2307,67 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="186">
+      <c r="E3" s="208">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="186"/>
+      <c r="F3" s="208"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="D4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="D5" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="J5" s="160"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J5" s="159"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-      <c r="D6" s="187" t="s">
-        <v>156</v>
-      </c>
-      <c r="E6" s="187"/>
-      <c r="F6" s="187"/>
-      <c r="G6" s="187"/>
-      <c r="H6" s="188"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D6" s="209" t="s">
+        <v>145</v>
+      </c>
+      <c r="E6" s="209"/>
+      <c r="F6" s="209"/>
+      <c r="G6" s="209"/>
+      <c r="H6" s="210"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="D7" s="187"/>
-      <c r="E7" s="187"/>
-      <c r="F7" s="187"/>
-      <c r="G7" s="187"/>
-      <c r="H7" s="188"/>
-    </row>
-    <row r="8" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="209"/>
+      <c r="E7" s="209"/>
+      <c r="F7" s="209"/>
+      <c r="G7" s="209"/>
+      <c r="H7" s="210"/>
+    </row>
+    <row r="8" spans="1:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
-      <c r="D8" s="187"/>
-      <c r="E8" s="187"/>
-      <c r="F8" s="187"/>
-      <c r="G8" s="187"/>
-      <c r="H8" s="188"/>
-    </row>
-    <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D8" s="209"/>
+      <c r="E8" s="209"/>
+      <c r="F8" s="209"/>
+      <c r="G8" s="209"/>
+      <c r="H8" s="210"/>
+    </row>
+    <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>3</v>
       </c>
@@ -2401,15 +2375,15 @@
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
       <c r="E9" s="10" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="11"/>
-      <c r="H9" s="163" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H9" s="162" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -2419,20 +2393,20 @@
       <c r="G10" s="1"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2442,453 +2416,388 @@
       <c r="G13" s="2"/>
       <c r="H13" s="8"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="194" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="222" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="194"/>
-      <c r="C14" s="194"/>
-      <c r="D14" s="194"/>
-      <c r="E14" s="194"/>
-      <c r="F14" s="194"/>
-      <c r="G14" s="194"/>
-      <c r="H14" s="194"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="252"/>
-      <c r="B15" s="253"/>
-      <c r="C15" s="253"/>
-      <c r="D15" s="253"/>
-      <c r="E15" s="253"/>
-      <c r="F15" s="253"/>
-      <c r="G15" s="253"/>
-      <c r="H15" s="254"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="252" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="253" t="s">
-        <v>140</v>
-      </c>
-      <c r="C16" s="253"/>
-      <c r="D16" s="253"/>
-      <c r="E16" s="253"/>
-      <c r="F16" s="253"/>
-      <c r="G16" s="253"/>
-      <c r="H16" s="255">
+      <c r="B14" s="222"/>
+      <c r="C14" s="222"/>
+      <c r="D14" s="222"/>
+      <c r="E14" s="222"/>
+      <c r="F14" s="222"/>
+      <c r="G14" s="222"/>
+      <c r="H14" s="222"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="H15" s="186"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>129</v>
+      </c>
+      <c r="H16" s="187">
         <f>392270+392270*2%</f>
         <v>400115.4</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="256" t="s">
-        <v>158</v>
-      </c>
-      <c r="B17" s="253"/>
-      <c r="C17" s="253"/>
-      <c r="D17" s="253"/>
-      <c r="E17" s="253"/>
-      <c r="F17" s="253"/>
-      <c r="G17" s="253"/>
-      <c r="H17" s="255">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="188" t="s">
+        <v>147</v>
+      </c>
+      <c r="H17" s="187">
         <v>4030.28</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="257" t="s">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="189" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="258"/>
-      <c r="C18" s="258"/>
-      <c r="D18" s="258"/>
-      <c r="E18" s="258"/>
-      <c r="F18" s="258"/>
-      <c r="G18" s="258"/>
-      <c r="H18" s="259">
+      <c r="B18" s="190"/>
+      <c r="C18" s="190"/>
+      <c r="D18" s="190"/>
+      <c r="E18" s="190"/>
+      <c r="F18" s="190"/>
+      <c r="G18" s="190"/>
+      <c r="H18" s="191">
         <f>SUM(H15:H17)</f>
         <v>404145.68000000005</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="260"/>
-      <c r="B19" s="261"/>
-      <c r="C19" s="261"/>
-      <c r="D19" s="261"/>
-      <c r="E19" s="261"/>
-      <c r="F19" s="261"/>
-      <c r="G19" s="261"/>
-      <c r="H19" s="262"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="263" t="s">
+    <row r="19" spans="1:10" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="223" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="264"/>
-      <c r="C20" s="264"/>
-      <c r="D20" s="264"/>
-      <c r="E20" s="264"/>
-      <c r="F20" s="264"/>
-      <c r="G20" s="264"/>
-      <c r="H20" s="265"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="252" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="253"/>
-      <c r="C21" s="266"/>
-      <c r="D21" s="253"/>
-      <c r="E21" s="253"/>
-      <c r="F21" s="253"/>
-      <c r="G21" s="253"/>
-      <c r="H21" s="267">
+      <c r="B20" s="224"/>
+      <c r="C20" s="224"/>
+      <c r="D20" s="224"/>
+      <c r="E20" s="224"/>
+      <c r="F20" s="224"/>
+      <c r="G20" s="224"/>
+      <c r="H20" s="225"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="192"/>
+      <c r="H21" s="193">
         <v>17336.11</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="252" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="253"/>
-      <c r="C22" s="266"/>
-      <c r="D22" s="253"/>
-      <c r="E22" s="253"/>
-      <c r="F22" s="253"/>
-      <c r="G22" s="253"/>
-      <c r="H22" s="267">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="257" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="192"/>
+      <c r="H22" s="193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="189" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="258"/>
-      <c r="C23" s="258"/>
-      <c r="D23" s="258"/>
-      <c r="E23" s="258"/>
-      <c r="F23" s="258"/>
-      <c r="G23" s="258"/>
-      <c r="H23" s="268">
+      <c r="B23" s="190"/>
+      <c r="C23" s="190"/>
+      <c r="D23" s="190"/>
+      <c r="E23" s="190"/>
+      <c r="F23" s="190"/>
+      <c r="G23" s="190"/>
+      <c r="H23" s="194">
         <f>SUM(H21:H22)</f>
         <v>17336.11</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="194" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="194"/>
-      <c r="C24" s="194"/>
-      <c r="D24" s="194"/>
-      <c r="E24" s="194"/>
-      <c r="F24" s="194"/>
-      <c r="G24" s="194"/>
-      <c r="H24" s="194"/>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="222" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="222"/>
+      <c r="C24" s="222"/>
+      <c r="D24" s="222"/>
+      <c r="E24" s="222"/>
+      <c r="F24" s="222"/>
+      <c r="G24" s="222"/>
+      <c r="H24" s="222"/>
       <c r="J24" s="18"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="256" t="s">
-        <v>168</v>
-      </c>
-      <c r="B25" s="253"/>
-      <c r="C25" s="266"/>
-      <c r="D25" s="253"/>
-      <c r="E25" s="253"/>
-      <c r="F25" s="253"/>
-      <c r="G25" s="253"/>
-      <c r="H25" s="267">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="188" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" s="192"/>
+      <c r="H25" s="193">
         <v>48079.519999999997</v>
       </c>
       <c r="I25" s="13"/>
       <c r="J25" s="13"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="256" t="s">
-        <v>160</v>
-      </c>
-      <c r="B26" s="253"/>
-      <c r="C26" s="266"/>
-      <c r="D26" s="253"/>
-      <c r="E26" s="253"/>
-      <c r="F26" s="253"/>
-      <c r="G26" s="253"/>
-      <c r="H26" s="267">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="188" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" s="192"/>
+      <c r="H26" s="193">
         <v>0</v>
       </c>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="256" t="s">
-        <v>166</v>
-      </c>
-      <c r="B27" s="253"/>
-      <c r="C27" s="266"/>
-      <c r="D27" s="253"/>
-      <c r="E27" s="253"/>
-      <c r="F27" s="253"/>
-      <c r="G27" s="253"/>
-      <c r="H27" s="267">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="188" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" s="192"/>
+      <c r="H27" s="193">
         <v>20000</v>
       </c>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
     </row>
-    <row r="28" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="256" t="s">
-        <v>141</v>
-      </c>
-      <c r="B28" s="253"/>
-      <c r="C28" s="253"/>
-      <c r="D28" s="253"/>
-      <c r="E28" s="253"/>
-      <c r="F28" s="253"/>
-      <c r="G28" s="253"/>
-      <c r="H28" s="267">
+    <row r="28" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="188" t="s">
+        <v>130</v>
+      </c>
+      <c r="H28" s="193">
         <v>80000</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="257" t="s">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="189" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="258"/>
-      <c r="C29" s="258"/>
-      <c r="D29" s="258"/>
-      <c r="E29" s="258"/>
-      <c r="F29" s="258"/>
-      <c r="G29" s="258"/>
-      <c r="H29" s="268">
+      <c r="B29" s="190"/>
+      <c r="C29" s="190"/>
+      <c r="D29" s="190"/>
+      <c r="E29" s="190"/>
+      <c r="F29" s="190"/>
+      <c r="G29" s="190"/>
+      <c r="H29" s="194">
         <f>SUM(H25:H28)</f>
         <v>148079.51999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="263" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="264"/>
-      <c r="C30" s="264"/>
-      <c r="D30" s="264"/>
-      <c r="E30" s="264"/>
-      <c r="F30" s="264"/>
-      <c r="G30" s="264"/>
-      <c r="H30" s="265"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="252" t="s">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="223" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="224"/>
+      <c r="C30" s="224"/>
+      <c r="D30" s="224"/>
+      <c r="E30" s="224"/>
+      <c r="F30" s="224"/>
+      <c r="G30" s="224"/>
+      <c r="H30" s="225"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="253"/>
-      <c r="C31" s="253" t="s">
+      <c r="C31" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="253"/>
-      <c r="E31" s="253"/>
-      <c r="F31" s="253"/>
-      <c r="G31" s="253"/>
-      <c r="H31" s="269">
+      <c r="H31" s="195">
         <v>97600</v>
       </c>
       <c r="I31" s="31"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="252" t="s">
-        <v>169</v>
-      </c>
-      <c r="B32" s="253"/>
-      <c r="C32" s="253"/>
-      <c r="D32" s="253"/>
-      <c r="E32" s="253"/>
-      <c r="F32" s="253"/>
-      <c r="G32" s="253"/>
-      <c r="H32" s="269">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H32" s="195">
         <v>0</v>
       </c>
       <c r="I32" s="31"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="257" t="s">
-        <v>159</v>
-      </c>
-      <c r="B33" s="258"/>
-      <c r="C33" s="258"/>
-      <c r="D33" s="258"/>
-      <c r="E33" s="258"/>
-      <c r="F33" s="258"/>
-      <c r="G33" s="258"/>
-      <c r="H33" s="270">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="189" t="s">
+        <v>148</v>
+      </c>
+      <c r="B33" s="190"/>
+      <c r="C33" s="190"/>
+      <c r="D33" s="190"/>
+      <c r="E33" s="190"/>
+      <c r="F33" s="190"/>
+      <c r="G33" s="190"/>
+      <c r="H33" s="196">
         <f>SUM(H31:H32)</f>
         <v>97600</v>
       </c>
       <c r="I33" s="31"/>
       <c r="N33" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="252"/>
-      <c r="B34" s="253"/>
-      <c r="C34" s="253"/>
-      <c r="D34" s="253"/>
-      <c r="E34" s="253"/>
-      <c r="F34" s="253"/>
-      <c r="G34" s="253"/>
-      <c r="H34" s="271"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="263" t="s">
-        <v>161</v>
-      </c>
-      <c r="B35" s="264"/>
-      <c r="C35" s="264"/>
-      <c r="D35" s="264"/>
-      <c r="E35" s="264"/>
-      <c r="F35" s="264"/>
-      <c r="G35" s="264"/>
-      <c r="H35" s="265"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="272" t="s">
-        <v>162</v>
-      </c>
-      <c r="B36" s="273"/>
-      <c r="C36" s="273"/>
-      <c r="D36" s="273"/>
-      <c r="E36" s="273"/>
-      <c r="F36" s="273"/>
-      <c r="G36" s="273"/>
-      <c r="H36" s="274">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="5"/>
+      <c r="H34" s="197"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="223" t="s">
+        <v>150</v>
+      </c>
+      <c r="B35" s="224"/>
+      <c r="C35" s="224"/>
+      <c r="D35" s="224"/>
+      <c r="E35" s="224"/>
+      <c r="F35" s="224"/>
+      <c r="G35" s="224"/>
+      <c r="H35" s="225"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="198" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="199"/>
+      <c r="C36" s="199"/>
+      <c r="D36" s="199"/>
+      <c r="E36" s="199"/>
+      <c r="F36" s="199"/>
+      <c r="G36" s="199"/>
+      <c r="H36" s="200">
         <v>19863.259999999998</v>
       </c>
       <c r="J36" s="14"/>
     </row>
-    <row r="37" spans="1:14" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="275" t="s">
+    <row r="37" spans="1:14" s="15" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="201" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="276"/>
-      <c r="C37" s="276"/>
-      <c r="D37" s="276"/>
-      <c r="E37" s="276"/>
-      <c r="F37" s="276"/>
-      <c r="G37" s="276"/>
-      <c r="H37" s="277">
+      <c r="B37" s="202"/>
+      <c r="C37" s="202"/>
+      <c r="D37" s="202"/>
+      <c r="E37" s="202"/>
+      <c r="F37" s="202"/>
+      <c r="G37" s="202"/>
+      <c r="H37" s="203">
         <f>H18+H23+H29+H33+H36</f>
         <v>687024.57000000007</v>
       </c>
     </row>
-    <row r="38" spans="1:14" s="13" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="278" t="s">
-        <v>170</v>
-      </c>
-      <c r="B38" s="279"/>
-      <c r="C38" s="279"/>
-      <c r="D38" s="279"/>
-      <c r="E38" s="279"/>
-      <c r="F38" s="279"/>
-      <c r="G38" s="279"/>
-      <c r="H38" s="280">
+    <row r="38" spans="1:14" s="13" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A38" s="204" t="s">
+        <v>159</v>
+      </c>
+      <c r="B38" s="205"/>
+      <c r="C38" s="205"/>
+      <c r="D38" s="205"/>
+      <c r="E38" s="205"/>
+      <c r="F38" s="205"/>
+      <c r="G38" s="205"/>
+      <c r="H38" s="206">
         <v>500000</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="281" t="s">
+    <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="213" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="282"/>
-      <c r="C39" s="282"/>
-      <c r="D39" s="282"/>
-      <c r="E39" s="282"/>
-      <c r="F39" s="282"/>
-      <c r="G39" s="282"/>
-      <c r="H39" s="283"/>
-      <c r="I39" s="142"/>
-      <c r="K39" s="142"/>
-    </row>
-    <row r="40" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="284"/>
-      <c r="B40" s="285"/>
-      <c r="C40" s="285"/>
-      <c r="D40" s="285"/>
-      <c r="E40" s="285"/>
-      <c r="F40" s="285"/>
-      <c r="G40" s="285"/>
-      <c r="H40" s="286"/>
-    </row>
-    <row r="41" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="287" t="s">
-        <v>167</v>
-      </c>
-      <c r="B41" s="288"/>
-      <c r="C41" s="288"/>
-      <c r="D41" s="288"/>
-      <c r="E41" s="288"/>
-      <c r="F41" s="288"/>
-      <c r="G41" s="289"/>
-      <c r="H41" s="290">
+      <c r="B39" s="214"/>
+      <c r="C39" s="214"/>
+      <c r="D39" s="214"/>
+      <c r="E39" s="214"/>
+      <c r="F39" s="214"/>
+      <c r="G39" s="214"/>
+      <c r="H39" s="215"/>
+      <c r="I39" s="141"/>
+      <c r="K39" s="141"/>
+    </row>
+    <row r="40" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="216"/>
+      <c r="B40" s="217"/>
+      <c r="C40" s="217"/>
+      <c r="D40" s="217"/>
+      <c r="E40" s="217"/>
+      <c r="F40" s="217"/>
+      <c r="G40" s="217"/>
+      <c r="H40" s="218"/>
+    </row>
+    <row r="41" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="232" t="s">
+        <v>156</v>
+      </c>
+      <c r="B41" s="233"/>
+      <c r="C41" s="233"/>
+      <c r="D41" s="233"/>
+      <c r="E41" s="233"/>
+      <c r="F41" s="233"/>
+      <c r="G41" s="234"/>
+      <c r="H41" s="207">
         <f>520000-350000</f>
         <v>170000</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="195"/>
-      <c r="B42" s="196"/>
-      <c r="C42" s="196"/>
-      <c r="D42" s="196"/>
-      <c r="E42" s="196"/>
-      <c r="F42" s="196"/>
-      <c r="G42" s="197"/>
+    <row r="42" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="226"/>
+      <c r="B42" s="227"/>
+      <c r="C42" s="227"/>
+      <c r="D42" s="227"/>
+      <c r="E42" s="227"/>
+      <c r="F42" s="227"/>
+      <c r="G42" s="228"/>
       <c r="H42" s="22"/>
     </row>
-    <row r="43" spans="1:14" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="198" t="s">
+    <row r="43" spans="1:14" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="229" t="s">
         <v>16</v>
       </c>
-      <c r="B43" s="199"/>
-      <c r="C43" s="199"/>
-      <c r="D43" s="199"/>
-      <c r="E43" s="199"/>
-      <c r="F43" s="199"/>
-      <c r="G43" s="200"/>
+      <c r="B43" s="230"/>
+      <c r="C43" s="230"/>
+      <c r="D43" s="230"/>
+      <c r="E43" s="230"/>
+      <c r="F43" s="230"/>
+      <c r="G43" s="231"/>
       <c r="H43" s="23">
         <f>SUM(H41:H42)</f>
         <v>170000</v>
       </c>
     </row>
-    <row r="44" spans="1:14" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="158"/>
-      <c r="B44" s="158"/>
-      <c r="C44" s="158"/>
-      <c r="D44" s="158"/>
-      <c r="E44" s="158"/>
-      <c r="F44" s="158"/>
-      <c r="G44" s="158"/>
-      <c r="H44" s="159"/>
-    </row>
-    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="157"/>
+      <c r="B44" s="157"/>
+      <c r="C44" s="157"/>
+      <c r="D44" s="157"/>
+      <c r="E44" s="157"/>
+      <c r="F44" s="157"/>
+      <c r="G44" s="157"/>
+      <c r="H44" s="158"/>
+    </row>
+    <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H45" s="17"/>
       <c r="J45" s="14"/>
     </row>
-    <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="189" t="s">
-        <v>142</v>
-      </c>
-      <c r="B46" s="189"/>
-      <c r="C46" s="189"/>
-      <c r="D46" s="189"/>
-      <c r="E46" s="189"/>
-      <c r="F46" s="189"/>
-      <c r="G46" s="189"/>
+    <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="211" t="s">
+        <v>131</v>
+      </c>
+      <c r="B46" s="211"/>
+      <c r="C46" s="211"/>
+      <c r="D46" s="211"/>
+      <c r="E46" s="211"/>
+      <c r="F46" s="211"/>
+      <c r="G46" s="211"/>
       <c r="H46" s="21">
         <f>+H37+H38</f>
         <v>1187024.57</v>
       </c>
-      <c r="J46" s="142"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J46" s="141"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="17"/>
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
@@ -2898,9 +2807,9 @@
       <c r="G47" s="17"/>
       <c r="H47" s="17"/>
     </row>
-    <row r="48" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="19" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
@@ -2913,7 +2822,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="17"/>
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
@@ -2923,35 +2832,35 @@
       <c r="G49" s="17"/>
       <c r="H49" s="17"/>
     </row>
-    <row r="50" spans="1:10" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="191" t="s">
+    <row r="50" spans="1:10" ht="18" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="219" t="s">
         <v>13</v>
       </c>
-      <c r="B50" s="192"/>
-      <c r="C50" s="192"/>
-      <c r="D50" s="192"/>
-      <c r="E50" s="192"/>
-      <c r="F50" s="192"/>
-      <c r="G50" s="192"/>
-      <c r="H50" s="193"/>
-    </row>
-    <row r="51" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="190" t="s">
-        <v>148</v>
-      </c>
-      <c r="B51" s="190"/>
-      <c r="C51" s="190"/>
-      <c r="D51" s="190"/>
-      <c r="E51" s="190"/>
-      <c r="F51" s="190"/>
-      <c r="G51" s="190"/>
+      <c r="B50" s="220"/>
+      <c r="C50" s="220"/>
+      <c r="D50" s="220"/>
+      <c r="E50" s="220"/>
+      <c r="F50" s="220"/>
+      <c r="G50" s="220"/>
+      <c r="H50" s="221"/>
+    </row>
+    <row r="51" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="212" t="s">
+        <v>137</v>
+      </c>
+      <c r="B51" s="212"/>
+      <c r="C51" s="212"/>
+      <c r="D51" s="212"/>
+      <c r="E51" s="212"/>
+      <c r="F51" s="212"/>
+      <c r="G51" s="212"/>
       <c r="H51" s="30">
         <v>1627667.8413207317</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="25" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B52" s="26"/>
       <c r="C52" s="26"/>
@@ -2961,12 +2870,12 @@
       <c r="G52" s="26"/>
       <c r="H52" s="32">
         <f>Planilla!I31</f>
-        <v>2437353.3800000008</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2458640.5300000007</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="25" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B53" s="26"/>
       <c r="C53" s="26"/>
@@ -2974,13 +2883,13 @@
       <c r="E53" s="26"/>
       <c r="F53" s="26"/>
       <c r="G53" s="26"/>
-      <c r="H53" s="216">
+      <c r="H53" s="169">
         <v>-4586</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="25" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B54" s="26"/>
       <c r="C54" s="26"/>
@@ -2994,7 +2903,7 @@
       </c>
       <c r="J54" s="14"/>
     </row>
-    <row r="55" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A55" s="28" t="s">
         <v>14</v>
       </c>
@@ -3006,7 +2915,7 @@
       <c r="G55" s="29"/>
       <c r="H55" s="33">
         <f>SUM(H51:H54)</f>
-        <v>3203410.6513207322</v>
+        <v>3224697.8013207326</v>
       </c>
     </row>
   </sheetData>
@@ -3038,193 +2947,193 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" style="34" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" style="36" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" style="35" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" style="35" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" style="35" customWidth="1"/>
-    <col min="10" max="10" width="2.85546875" style="35" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" style="35" customWidth="1"/>
-    <col min="12" max="12" width="0.140625" style="35" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" customWidth="1"/>
-    <col min="15" max="15" width="12.140625" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.44140625" style="34" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="36" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="35" customWidth="1"/>
+    <col min="8" max="8" width="7.5546875" style="35" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" style="35" customWidth="1"/>
+    <col min="10" max="10" width="0.44140625" style="35" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" style="35" customWidth="1"/>
+    <col min="12" max="12" width="0.109375" style="35" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="12.109375" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.28515625" customWidth="1"/>
+    <col min="18" max="18" width="13.33203125" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
     <col min="20" max="20" width="12" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="166" t="str">
+    <row r="1" spans="1:20" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="236" t="str">
         <f>Gastos!E9</f>
         <v xml:space="preserve">PERIODO: OCTUBRE </v>
       </c>
-      <c r="B1" s="167"/>
-      <c r="C1" s="167"/>
-      <c r="D1" s="167"/>
-      <c r="E1" s="167"/>
-      <c r="F1" s="167"/>
-      <c r="G1" s="167"/>
-      <c r="H1" s="167"/>
-      <c r="I1" s="167"/>
-      <c r="J1" s="167"/>
-      <c r="K1" s="167"/>
-      <c r="L1" s="167"/>
-      <c r="M1" s="167"/>
-      <c r="N1" s="167"/>
-      <c r="O1" s="167"/>
-      <c r="P1" s="167"/>
-      <c r="Q1" s="167"/>
-      <c r="R1" s="167"/>
-      <c r="S1" s="168"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B1" s="237"/>
+      <c r="C1" s="237"/>
+      <c r="D1" s="237"/>
+      <c r="E1" s="237"/>
+      <c r="F1" s="237"/>
+      <c r="G1" s="237"/>
+      <c r="H1" s="237"/>
+      <c r="I1" s="237"/>
+      <c r="J1" s="237"/>
+      <c r="K1" s="237"/>
+      <c r="L1" s="237"/>
+      <c r="M1" s="237"/>
+      <c r="N1" s="237"/>
+      <c r="O1" s="237"/>
+      <c r="P1" s="237"/>
+      <c r="Q1" s="237"/>
+      <c r="R1" s="237"/>
+      <c r="S1" s="238"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="69"/>
-      <c r="C2" s="155">
+      <c r="C2" s="154">
         <f>687024.57+500000</f>
         <v>1187024.5699999998</v>
       </c>
-      <c r="F2" s="234" t="s">
-        <v>174</v>
-      </c>
-      <c r="G2" s="235"/>
-      <c r="H2" s="235"/>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="236"/>
+      <c r="F2" s="256" t="s">
+        <v>163</v>
+      </c>
+      <c r="G2" s="257"/>
+      <c r="H2" s="257"/>
+      <c r="I2" s="257"/>
+      <c r="J2" s="257"/>
+      <c r="K2" s="258"/>
       <c r="L2" s="12"/>
-      <c r="M2" s="176" t="s">
-        <v>164</v>
-      </c>
-      <c r="N2" s="177"/>
-      <c r="O2" s="177"/>
-      <c r="P2" s="177"/>
-      <c r="Q2" s="177"/>
-      <c r="R2" s="177"/>
-      <c r="S2" s="178"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M2" s="246" t="s">
+        <v>153</v>
+      </c>
+      <c r="N2" s="247"/>
+      <c r="O2" s="247"/>
+      <c r="P2" s="247"/>
+      <c r="Q2" s="247"/>
+      <c r="R2" s="247"/>
+      <c r="S2" s="248"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="65"/>
-      <c r="D3" s="155">
+      <c r="D3" s="154">
         <v>500000</v>
       </c>
-      <c r="F3" s="237"/>
-      <c r="G3" s="238"/>
-      <c r="H3" s="238"/>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="239"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="260"/>
+      <c r="H3" s="260"/>
+      <c r="I3" s="260"/>
+      <c r="J3" s="260"/>
+      <c r="K3" s="261"/>
       <c r="L3" s="67"/>
-      <c r="M3" s="179"/>
-      <c r="N3" s="180"/>
-      <c r="O3" s="180"/>
-      <c r="P3" s="180"/>
-      <c r="Q3" s="180"/>
-      <c r="R3" s="180"/>
-      <c r="S3" s="181"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M3" s="249"/>
+      <c r="N3" s="250"/>
+      <c r="O3" s="250"/>
+      <c r="P3" s="250"/>
+      <c r="Q3" s="250"/>
+      <c r="R3" s="250"/>
+      <c r="S3" s="251"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="65"/>
-      <c r="C4" s="185" t="s">
-        <v>154</v>
-      </c>
-      <c r="D4" s="185"/>
-      <c r="F4" s="237"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="239"/>
+      <c r="C4" s="255" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="255"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="260"/>
+      <c r="H4" s="260"/>
+      <c r="I4" s="260"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="261"/>
       <c r="L4" s="67"/>
-      <c r="M4" s="179"/>
-      <c r="N4" s="180"/>
-      <c r="O4" s="180"/>
-      <c r="P4" s="180"/>
-      <c r="Q4" s="180"/>
-      <c r="R4" s="180"/>
-      <c r="S4" s="181"/>
-    </row>
-    <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M4" s="249"/>
+      <c r="N4" s="250"/>
+      <c r="O4" s="250"/>
+      <c r="P4" s="250"/>
+      <c r="Q4" s="250"/>
+      <c r="R4" s="250"/>
+      <c r="S4" s="251"/>
+    </row>
+    <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="65"/>
       <c r="B5" s="68"/>
-      <c r="C5" s="174">
+      <c r="C5" s="244">
         <f>D3</f>
         <v>500000</v>
       </c>
-      <c r="D5" s="174"/>
+      <c r="D5" s="244"/>
       <c r="E5" s="12"/>
-      <c r="F5" s="240"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="242"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="263"/>
+      <c r="H5" s="263"/>
+      <c r="I5" s="263"/>
+      <c r="J5" s="263"/>
+      <c r="K5" s="264"/>
       <c r="L5" s="67"/>
-      <c r="M5" s="179"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
-      <c r="P5" s="180"/>
-      <c r="Q5" s="180"/>
-      <c r="R5" s="180"/>
-      <c r="S5" s="181"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M5" s="249"/>
+      <c r="N5" s="250"/>
+      <c r="O5" s="250"/>
+      <c r="P5" s="250"/>
+      <c r="Q5" s="250"/>
+      <c r="R5" s="250"/>
+      <c r="S5" s="251"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="65"/>
       <c r="C6" s="12" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
-      <c r="F6" s="243" t="s">
-        <v>175</v>
-      </c>
-      <c r="G6" s="244"/>
-      <c r="H6" s="244"/>
-      <c r="I6" s="244"/>
-      <c r="J6" s="244"/>
-      <c r="K6" s="245"/>
+      <c r="F6" s="265" t="s">
+        <v>164</v>
+      </c>
+      <c r="G6" s="266"/>
+      <c r="H6" s="266"/>
+      <c r="I6" s="266"/>
+      <c r="J6" s="266"/>
+      <c r="K6" s="267"/>
       <c r="L6" s="37"/>
-      <c r="M6" s="179"/>
-      <c r="N6" s="180"/>
-      <c r="O6" s="180"/>
-      <c r="P6" s="180"/>
-      <c r="Q6" s="180"/>
-      <c r="R6" s="180"/>
-      <c r="S6" s="181"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M6" s="249"/>
+      <c r="N6" s="250"/>
+      <c r="O6" s="250"/>
+      <c r="P6" s="250"/>
+      <c r="Q6" s="250"/>
+      <c r="R6" s="250"/>
+      <c r="S6" s="251"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="65"/>
       <c r="B7" s="64"/>
-      <c r="C7" s="174">
+      <c r="C7" s="244">
         <f>C2-D3</f>
         <v>687024.56999999983</v>
       </c>
-      <c r="D7" s="174"/>
+      <c r="D7" s="244"/>
       <c r="E7" s="66"/>
-      <c r="F7" s="246"/>
-      <c r="G7" s="247"/>
-      <c r="H7" s="247"/>
-      <c r="I7" s="247"/>
-      <c r="J7" s="247"/>
-      <c r="K7" s="248"/>
+      <c r="F7" s="268"/>
+      <c r="G7" s="269"/>
+      <c r="H7" s="269"/>
+      <c r="I7" s="269"/>
+      <c r="J7" s="269"/>
+      <c r="K7" s="270"/>
       <c r="L7" s="37"/>
-      <c r="M7" s="179"/>
-      <c r="N7" s="180"/>
-      <c r="O7" s="180"/>
-      <c r="P7" s="180"/>
-      <c r="Q7" s="180"/>
-      <c r="R7" s="180"/>
-      <c r="S7" s="181"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M7" s="249"/>
+      <c r="N7" s="250"/>
+      <c r="O7" s="250"/>
+      <c r="P7" s="250"/>
+      <c r="Q7" s="250"/>
+      <c r="R7" s="250"/>
+      <c r="S7" s="251"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="65"/>
       <c r="B8" s="64"/>
       <c r="C8" s="64" t="s">
@@ -3232,45 +3141,45 @@
       </c>
       <c r="D8" s="64"/>
       <c r="E8" s="64"/>
-      <c r="F8" s="246"/>
-      <c r="G8" s="247"/>
-      <c r="H8" s="247"/>
-      <c r="I8" s="247"/>
-      <c r="J8" s="247"/>
-      <c r="K8" s="248"/>
+      <c r="F8" s="268"/>
+      <c r="G8" s="269"/>
+      <c r="H8" s="269"/>
+      <c r="I8" s="269"/>
+      <c r="J8" s="269"/>
+      <c r="K8" s="270"/>
       <c r="L8" s="37"/>
-      <c r="M8" s="179"/>
-      <c r="N8" s="180"/>
-      <c r="O8" s="180"/>
-      <c r="P8" s="180"/>
-      <c r="Q8" s="180"/>
-      <c r="R8" s="180"/>
-      <c r="S8" s="181"/>
-    </row>
-    <row r="9" spans="1:22" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="249"/>
+      <c r="N8" s="250"/>
+      <c r="O8" s="250"/>
+      <c r="P8" s="250"/>
+      <c r="Q8" s="250"/>
+      <c r="R8" s="250"/>
+      <c r="S8" s="251"/>
+    </row>
+    <row r="9" spans="1:20" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="63"/>
       <c r="B9" s="62"/>
-      <c r="C9" s="175">
+      <c r="C9" s="245">
         <v>170000</v>
       </c>
-      <c r="D9" s="175"/>
+      <c r="D9" s="245"/>
       <c r="E9" s="61"/>
-      <c r="F9" s="249"/>
-      <c r="G9" s="250"/>
-      <c r="H9" s="250"/>
-      <c r="I9" s="250"/>
-      <c r="J9" s="250"/>
-      <c r="K9" s="251"/>
+      <c r="F9" s="271"/>
+      <c r="G9" s="272"/>
+      <c r="H9" s="272"/>
+      <c r="I9" s="272"/>
+      <c r="J9" s="272"/>
+      <c r="K9" s="273"/>
       <c r="L9" s="60"/>
-      <c r="M9" s="182"/>
-      <c r="N9" s="183"/>
-      <c r="O9" s="183"/>
-      <c r="P9" s="183"/>
-      <c r="Q9" s="183"/>
-      <c r="R9" s="183"/>
-      <c r="S9" s="184"/>
-    </row>
-    <row r="10" spans="1:22" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="252"/>
+      <c r="N9" s="253"/>
+      <c r="O9" s="253"/>
+      <c r="P9" s="253"/>
+      <c r="Q9" s="253"/>
+      <c r="R9" s="253"/>
+      <c r="S9" s="254"/>
+    </row>
+    <row r="10" spans="1:20" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="59" t="s">
         <v>31</v>
       </c>
@@ -3290,7 +3199,7 @@
         <v>27</v>
       </c>
       <c r="G10" s="56" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="H10" s="56" t="s">
         <v>26</v>
@@ -3308,13 +3217,13 @@
         <v>22</v>
       </c>
       <c r="M10" s="55" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="N10" s="55" t="s">
         <v>21</v>
       </c>
       <c r="O10" s="55" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="P10" s="55" t="s">
         <v>20</v>
@@ -3327,31 +3236,31 @@
         <v>1ER vto - VTO: 15/12'</v>
       </c>
       <c r="S10" s="55" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="149" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="150"/>
-      <c r="C11" s="151" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="148" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="149"/>
+      <c r="C11" s="150" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="152" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" s="138"/>
-      <c r="F11" s="153">
+      <c r="D11" s="151" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="137"/>
+      <c r="F11" s="152">
         <v>7.9</v>
       </c>
-      <c r="G11" s="210">
+      <c r="G11" s="161">
         <v>150476.01</v>
       </c>
-      <c r="H11" s="210">
-        <v>0</v>
-      </c>
-      <c r="I11" s="211">
+      <c r="H11" s="161">
+        <v>0</v>
+      </c>
+      <c r="I11" s="164">
         <v>154990.01</v>
       </c>
       <c r="J11" s="48" t="e">
@@ -3363,11 +3272,11 @@
         <v>-4514</v>
       </c>
       <c r="L11" s="48"/>
-      <c r="M11" s="154">
+      <c r="M11" s="153">
         <f>(K11+L11)*3%</f>
         <v>-135.41999999999999</v>
       </c>
-      <c r="N11" s="154">
+      <c r="N11" s="153">
         <f t="shared" ref="N11:N19" si="1">K11+M11+L11</f>
         <v>-4649.42</v>
       </c>
@@ -3383,64 +3292,61 @@
         <f>C$5*F11/100</f>
         <v>39500</v>
       </c>
-      <c r="R11" s="162">
+      <c r="R11" s="161">
         <f>ROUND(O11+N11+P11+Q11,0) + T11</f>
         <v>102556.01</v>
       </c>
-      <c r="S11" s="161">
+      <c r="S11" s="160">
         <f>ROUND(R11+R11*3%,0) + T11</f>
         <v>105633.01</v>
       </c>
       <c r="T11" s="31">
         <v>0.01</v>
       </c>
-      <c r="V11" s="70" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="143" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="136"/>
-      <c r="C12" s="144" t="s">
+    </row>
+    <row r="12" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="142" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="135"/>
+      <c r="C12" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="145" t="s">
-        <v>99</v>
-      </c>
-      <c r="E12" s="146"/>
-      <c r="F12" s="147">
+      <c r="D12" s="144" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="145"/>
+      <c r="F12" s="146">
         <v>7.9</v>
       </c>
-      <c r="G12" s="211">
+      <c r="G12" s="164">
         <v>150476.01999999999</v>
       </c>
-      <c r="H12" s="211">
-        <v>0</v>
-      </c>
-      <c r="I12" s="211">
-        <f t="shared" ref="I11:I19" si="2">G12</f>
+      <c r="H12" s="164">
+        <v>0</v>
+      </c>
+      <c r="I12" s="164">
+        <f t="shared" ref="I12" si="2">G12</f>
         <v>150476.01999999999</v>
       </c>
-      <c r="J12" s="134" t="e">
+      <c r="J12" s="133" t="e">
         <f>C8*F12/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K12" s="134">
+      <c r="K12" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L12" s="134"/>
-      <c r="M12" s="140">
+      <c r="L12" s="133"/>
+      <c r="M12" s="139">
         <f t="shared" ref="M12:M29" si="3">(K12+L12)*3%</f>
         <v>0</v>
       </c>
-      <c r="N12" s="140">
+      <c r="N12" s="139">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O12" s="134">
+      <c r="O12" s="133">
         <f t="shared" ref="O12:O29" si="4">C$7*F12/100</f>
         <v>54274.941029999994</v>
       </c>
@@ -3452,11 +3358,11 @@
         <f t="shared" ref="Q12:Q22" si="6">C$5*F12/100</f>
         <v>39500</v>
       </c>
-      <c r="R12" s="162">
+      <c r="R12" s="161">
         <f t="shared" ref="R12:R29" si="7">ROUND(O12+N12+P12+Q12,0) + T12</f>
         <v>107205.02</v>
       </c>
-      <c r="S12" s="161">
+      <c r="S12" s="160">
         <f t="shared" ref="S12:S29" si="8">ROUND(R12+R12*3%,0) + T12</f>
         <v>110421.02</v>
       </c>
@@ -3464,52 +3370,49 @@
         <f t="shared" ref="T12:T29" si="9">T11+0.01</f>
         <v>0.02</v>
       </c>
-      <c r="V12" s="71" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="135" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="136"/>
-      <c r="C13" s="72" t="s">
+    </row>
+    <row r="13" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="134" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="135"/>
+      <c r="C13" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="137" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" s="138" t="s">
-        <v>108</v>
-      </c>
-      <c r="F13" s="139">
+      <c r="D13" s="136" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="137" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="138">
         <v>7.9</v>
       </c>
-      <c r="G13" s="210">
+      <c r="G13" s="161">
         <v>150476.03</v>
       </c>
-      <c r="H13" s="211">
-        <v>0</v>
-      </c>
-      <c r="I13" s="211"/>
-      <c r="J13" s="134" t="e">
+      <c r="H13" s="164">
+        <v>0</v>
+      </c>
+      <c r="I13" s="164"/>
+      <c r="J13" s="133" t="e">
         <f>C8*F13/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K13" s="134">
+      <c r="K13" s="133">
         <f t="shared" si="0"/>
         <v>150476.03</v>
       </c>
-      <c r="L13" s="134"/>
-      <c r="M13" s="140">
+      <c r="L13" s="133"/>
+      <c r="M13" s="139">
         <f t="shared" si="3"/>
         <v>4514.2808999999997</v>
       </c>
-      <c r="N13" s="140">
+      <c r="N13" s="139">
         <f t="shared" si="1"/>
         <v>154990.31090000001</v>
       </c>
-      <c r="O13" s="134">
+      <c r="O13" s="133">
         <f t="shared" si="4"/>
         <v>54274.941029999994</v>
       </c>
@@ -3521,11 +3424,11 @@
         <f t="shared" si="6"/>
         <v>39500</v>
       </c>
-      <c r="R13" s="162">
+      <c r="R13" s="161">
         <f t="shared" si="7"/>
         <v>262195.03000000003</v>
       </c>
-      <c r="S13" s="161">
+      <c r="S13" s="160">
         <f t="shared" si="8"/>
         <v>270061.03000000003</v>
       </c>
@@ -3533,30 +3436,27 @@
         <f t="shared" si="9"/>
         <v>0.03</v>
       </c>
-      <c r="V13" s="71" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="86" t="s">
-        <v>82</v>
+    </row>
+    <row r="14" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="85" t="s">
+        <v>71</v>
       </c>
       <c r="B14" s="54"/>
-      <c r="C14" s="71" t="s">
+      <c r="C14" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="132" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" s="89"/>
-      <c r="F14" s="73">
+      <c r="D14" s="131" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="88"/>
+      <c r="F14" s="72">
         <v>7.9</v>
       </c>
-      <c r="G14" s="212">
+      <c r="G14" s="165">
         <v>150476.04</v>
       </c>
-      <c r="H14" s="213"/>
-      <c r="I14" s="211">
+      <c r="H14" s="166"/>
+      <c r="I14" s="164">
         <v>154990.04</v>
       </c>
       <c r="J14" s="46" t="e">
@@ -3588,11 +3488,11 @@
         <f t="shared" si="6"/>
         <v>39500</v>
       </c>
-      <c r="R14" s="162">
+      <c r="R14" s="161">
         <f t="shared" si="7"/>
         <v>102556.04</v>
       </c>
-      <c r="S14" s="161">
+      <c r="S14" s="160">
         <f t="shared" si="8"/>
         <v>105633.04</v>
       </c>
@@ -3600,32 +3500,29 @@
         <f t="shared" si="9"/>
         <v>0.04</v>
       </c>
-      <c r="V14" s="71" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="86" t="s">
-        <v>83</v>
+    </row>
+    <row r="15" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="85" t="s">
+        <v>72</v>
       </c>
       <c r="B15" s="52"/>
-      <c r="C15" s="71" t="s">
+      <c r="C15" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="87" t="s">
-        <v>102</v>
-      </c>
-      <c r="E15" s="89"/>
-      <c r="F15" s="73">
+      <c r="D15" s="86" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="88"/>
+      <c r="F15" s="72">
         <v>7.9</v>
       </c>
-      <c r="G15" s="214">
+      <c r="G15" s="167">
         <v>150476.04999999999</v>
       </c>
-      <c r="H15" s="213">
-        <v>0</v>
-      </c>
-      <c r="I15" s="211">
+      <c r="H15" s="166">
+        <v>0</v>
+      </c>
+      <c r="I15" s="164">
         <f>154990.05</f>
         <v>154990.04999999999</v>
       </c>
@@ -3658,11 +3555,11 @@
         <f t="shared" si="6"/>
         <v>39500</v>
       </c>
-      <c r="R15" s="162">
+      <c r="R15" s="161">
         <f t="shared" si="7"/>
         <v>102556.05</v>
       </c>
-      <c r="S15" s="161">
+      <c r="S15" s="160">
         <f t="shared" si="8"/>
         <v>105633.05</v>
       </c>
@@ -3670,71 +3567,68 @@
         <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
-      <c r="V15" s="71" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="135" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="136"/>
-      <c r="C16" s="219" t="s">
+    </row>
+    <row r="16" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="134" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="135"/>
+      <c r="C16" s="172" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="220" t="s">
-        <v>155</v>
-      </c>
-      <c r="E16" s="221" t="s">
-        <v>163</v>
-      </c>
-      <c r="F16" s="222">
+      <c r="D16" s="173" t="s">
+        <v>144</v>
+      </c>
+      <c r="E16" s="174" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="175">
         <v>7.9</v>
       </c>
-      <c r="G16" s="223">
+      <c r="G16" s="176">
         <v>150476.06</v>
       </c>
-      <c r="H16" s="224">
-        <v>0</v>
-      </c>
-      <c r="I16" s="224">
+      <c r="H16" s="177">
+        <v>0</v>
+      </c>
+      <c r="I16" s="177">
         <f>163345-I28</f>
         <v>152748.82</v>
       </c>
-      <c r="J16" s="225" t="e">
+      <c r="J16" s="178" t="e">
         <f>C8*F16/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K16" s="225">
+      <c r="K16" s="178">
         <f t="shared" si="0"/>
         <v>-2272.7600000000093</v>
       </c>
-      <c r="L16" s="225"/>
-      <c r="M16" s="226">
+      <c r="L16" s="178"/>
+      <c r="M16" s="179">
         <f t="shared" si="3"/>
         <v>-68.18280000000027</v>
       </c>
-      <c r="N16" s="226">
+      <c r="N16" s="179">
         <f t="shared" si="1"/>
         <v>-2340.9428000000098</v>
       </c>
-      <c r="O16" s="225">
+      <c r="O16" s="178">
         <f t="shared" si="4"/>
         <v>54274.941029999994</v>
       </c>
-      <c r="P16" s="227">
+      <c r="P16" s="180">
         <f t="shared" si="5"/>
         <v>13430</v>
       </c>
-      <c r="Q16" s="227">
+      <c r="Q16" s="180">
         <f t="shared" si="6"/>
         <v>39500</v>
       </c>
-      <c r="R16" s="228">
+      <c r="R16" s="176">
         <f t="shared" si="7"/>
         <v>104864.06</v>
       </c>
-      <c r="S16" s="229">
+      <c r="S16" s="181">
         <f t="shared" si="8"/>
         <v>108010.06</v>
       </c>
@@ -3742,71 +3636,68 @@
         <f t="shared" si="9"/>
         <v>6.0000000000000005E-2</v>
       </c>
-      <c r="V16" s="71" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="86" t="s">
-        <v>85</v>
+    </row>
+    <row r="17" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="85" t="s">
+        <v>74</v>
       </c>
       <c r="B17" s="52"/>
-      <c r="C17" s="219" t="s">
+      <c r="C17" s="172" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="220" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" s="221" t="s">
-        <v>143</v>
-      </c>
-      <c r="F17" s="222">
+      <c r="D17" s="173" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="174" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17" s="175">
         <v>7.9</v>
       </c>
-      <c r="G17" s="223">
+      <c r="G17" s="176">
         <v>161167.07</v>
       </c>
-      <c r="H17" s="224">
-        <v>0</v>
-      </c>
-      <c r="I17" s="224">
+      <c r="H17" s="177">
+        <v>0</v>
+      </c>
+      <c r="I17" s="177">
         <f>176916.2-I23</f>
         <v>166320.07</v>
       </c>
-      <c r="J17" s="225" t="e">
+      <c r="J17" s="178" t="e">
         <f>C8*F17/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K17" s="225">
+      <c r="K17" s="178">
         <f t="shared" si="0"/>
         <v>-5153</v>
       </c>
-      <c r="L17" s="225"/>
-      <c r="M17" s="226">
+      <c r="L17" s="178"/>
+      <c r="M17" s="179">
         <f t="shared" si="3"/>
         <v>-154.59</v>
       </c>
-      <c r="N17" s="226">
+      <c r="N17" s="179">
         <f t="shared" si="1"/>
         <v>-5307.59</v>
       </c>
-      <c r="O17" s="225">
+      <c r="O17" s="178">
         <f t="shared" si="4"/>
         <v>54274.941029999994</v>
       </c>
-      <c r="P17" s="227">
+      <c r="P17" s="180">
         <f t="shared" si="5"/>
         <v>13430</v>
       </c>
-      <c r="Q17" s="227">
+      <c r="Q17" s="180">
         <f t="shared" si="6"/>
         <v>39500</v>
       </c>
-      <c r="R17" s="228">
+      <c r="R17" s="176">
         <f t="shared" si="7"/>
         <v>101897.07</v>
       </c>
-      <c r="S17" s="229">
+      <c r="S17" s="181">
         <f t="shared" si="8"/>
         <v>104954.07</v>
       </c>
@@ -3814,55 +3705,52 @@
         <f t="shared" si="9"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="V17" s="71" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="135" t="s">
-        <v>86</v>
-      </c>
-      <c r="B18" s="136"/>
-      <c r="C18" s="72" t="s">
+    </row>
+    <row r="18" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="134" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="135"/>
+      <c r="C18" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="137" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18" s="138" t="s">
-        <v>144</v>
-      </c>
-      <c r="F18" s="139">
+      <c r="D18" s="136" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" s="137" t="s">
+        <v>133</v>
+      </c>
+      <c r="F18" s="138">
         <v>7.9</v>
       </c>
-      <c r="G18" s="210">
+      <c r="G18" s="161">
         <v>308030.08000000002</v>
       </c>
-      <c r="H18" s="211">
-        <v>0</v>
-      </c>
-      <c r="I18" s="211">
+      <c r="H18" s="164">
+        <v>0</v>
+      </c>
+      <c r="I18" s="164">
         <f>G18</f>
         <v>308030.08000000002</v>
       </c>
-      <c r="J18" s="134" t="e">
+      <c r="J18" s="133" t="e">
         <f>C8*F18/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K18" s="134">
+      <c r="K18" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L18" s="134"/>
-      <c r="M18" s="140">
+      <c r="L18" s="133"/>
+      <c r="M18" s="139">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N18" s="140">
+      <c r="N18" s="139">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O18" s="134">
+      <c r="O18" s="133">
         <f t="shared" si="4"/>
         <v>54274.941029999994</v>
       </c>
@@ -3874,11 +3762,11 @@
         <f t="shared" si="6"/>
         <v>39500</v>
       </c>
-      <c r="R18" s="162">
+      <c r="R18" s="161">
         <f t="shared" si="7"/>
         <v>107205.08</v>
       </c>
-      <c r="S18" s="161">
+      <c r="S18" s="160">
         <f t="shared" si="8"/>
         <v>110421.08</v>
       </c>
@@ -3886,55 +3774,52 @@
         <f t="shared" si="9"/>
         <v>0.08</v>
       </c>
-      <c r="V18" s="71" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="135" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="136"/>
-      <c r="C19" s="72" t="s">
+    </row>
+    <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="134" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="135"/>
+      <c r="C19" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="137" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" s="138"/>
-      <c r="F19" s="139">
+      <c r="D19" s="136" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="137"/>
+      <c r="F19" s="138">
         <v>7.9</v>
       </c>
-      <c r="G19" s="210">
+      <c r="G19" s="161">
         <v>150476.09</v>
       </c>
-      <c r="H19" s="211">
-        <v>0</v>
-      </c>
-      <c r="I19" s="211">
+      <c r="H19" s="164">
+        <v>0</v>
+      </c>
+      <c r="I19" s="164">
         <v>154990.09</v>
       </c>
-      <c r="J19" s="134" t="e">
+      <c r="J19" s="133" t="e">
         <f>C8*F19/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K19" s="134">
+      <c r="K19" s="133">
         <f t="shared" ref="K19:K29" si="10">G19-H19-I19</f>
         <v>-4514</v>
       </c>
-      <c r="L19" s="134">
+      <c r="L19" s="133">
         <f>G19-I19</f>
         <v>-4514</v>
       </c>
-      <c r="M19" s="140">
+      <c r="M19" s="139">
         <f t="shared" si="3"/>
         <v>-270.83999999999997</v>
       </c>
-      <c r="N19" s="140">
+      <c r="N19" s="139">
         <f t="shared" si="1"/>
         <v>-9298.84</v>
       </c>
-      <c r="O19" s="134">
+      <c r="O19" s="133">
         <f t="shared" si="4"/>
         <v>54274.941029999994</v>
       </c>
@@ -3946,11 +3831,11 @@
         <f t="shared" si="6"/>
         <v>39500</v>
       </c>
-      <c r="R19" s="162">
+      <c r="R19" s="161">
         <f t="shared" si="7"/>
         <v>97906.09</v>
       </c>
-      <c r="S19" s="161">
+      <c r="S19" s="160">
         <f t="shared" si="8"/>
         <v>100843.09</v>
       </c>
@@ -3958,132 +3843,126 @@
         <f t="shared" si="9"/>
         <v>0.09</v>
       </c>
-      <c r="V19" s="71" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="217" t="s">
-        <v>88</v>
-      </c>
-      <c r="B20" s="136"/>
-      <c r="C20" s="219" t="s">
+    </row>
+    <row r="20" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="170" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" s="135"/>
+      <c r="C20" s="172" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="220" t="s">
-        <v>105</v>
-      </c>
-      <c r="E20" s="221"/>
-      <c r="F20" s="222">
+      <c r="D20" s="173" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="174"/>
+      <c r="F20" s="175">
         <v>7.9</v>
       </c>
-      <c r="G20" s="223">
+      <c r="G20" s="176">
         <v>308030.09999999998</v>
       </c>
-      <c r="H20" s="224"/>
-      <c r="I20" s="224">
+      <c r="H20" s="177"/>
+      <c r="I20" s="177">
         <f>142126+165904.25</f>
         <v>308030.25</v>
       </c>
-      <c r="J20" s="225"/>
-      <c r="K20" s="225">
+      <c r="J20" s="178"/>
+      <c r="K20" s="178">
         <f t="shared" si="10"/>
         <v>-0.15000000002328306</v>
       </c>
-      <c r="L20" s="225"/>
-      <c r="M20" s="226">
+      <c r="L20" s="178"/>
+      <c r="M20" s="179">
         <f t="shared" si="3"/>
         <v>-4.5000000006984921E-3</v>
       </c>
-      <c r="N20" s="226">
+      <c r="N20" s="179">
         <f t="shared" ref="N20:N29" si="11">K20+M20+L20</f>
         <v>-0.15450000002398157</v>
       </c>
-      <c r="O20" s="225">
+      <c r="O20" s="178">
         <f t="shared" si="4"/>
         <v>54274.941029999994</v>
       </c>
-      <c r="P20" s="227">
+      <c r="P20" s="180">
         <f t="shared" si="5"/>
         <v>13430</v>
       </c>
-      <c r="Q20" s="227">
+      <c r="Q20" s="180">
         <f t="shared" si="6"/>
         <v>39500</v>
       </c>
-      <c r="R20" s="228">
+      <c r="R20" s="176">
         <f t="shared" si="7"/>
         <v>107205.1</v>
       </c>
-      <c r="S20" s="229">
+      <c r="S20" s="181">
         <f t="shared" si="8"/>
         <v>110421.1</v>
       </c>
-      <c r="T20" s="164">
+      <c r="T20" s="163">
         <f t="shared" si="9"/>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="U20" s="13"/>
-      <c r="V20" s="71" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="217" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="136"/>
-      <c r="C21" s="219" t="s">
+    </row>
+    <row r="21" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="170" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="135"/>
+      <c r="C21" s="172" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="220" t="s">
-        <v>106</v>
-      </c>
-      <c r="E21" s="221" t="s">
-        <v>109</v>
-      </c>
-      <c r="F21" s="222">
+      <c r="D21" s="173" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="174" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" s="175">
         <v>7.9</v>
       </c>
-      <c r="G21" s="223">
+      <c r="G21" s="176">
         <v>308030.11</v>
       </c>
-      <c r="H21" s="224"/>
-      <c r="I21" s="224">
+      <c r="H21" s="177"/>
+      <c r="I21" s="177">
         <f>339197-I24</f>
         <v>317909.86</v>
       </c>
-      <c r="J21" s="225"/>
-      <c r="K21" s="225">
+      <c r="J21" s="178"/>
+      <c r="K21" s="178">
         <f t="shared" si="10"/>
         <v>-9879.75</v>
       </c>
-      <c r="L21" s="225"/>
-      <c r="M21" s="226">
+      <c r="L21" s="178"/>
+      <c r="M21" s="179">
         <f t="shared" si="3"/>
         <v>-296.39249999999998</v>
       </c>
-      <c r="N21" s="226">
+      <c r="N21" s="179">
         <f t="shared" si="11"/>
         <v>-10176.1425</v>
       </c>
-      <c r="O21" s="225">
+      <c r="O21" s="178">
         <f t="shared" si="4"/>
         <v>54274.941029999994</v>
       </c>
-      <c r="P21" s="227">
+      <c r="P21" s="180">
         <f t="shared" si="5"/>
         <v>13430</v>
       </c>
-      <c r="Q21" s="227">
+      <c r="Q21" s="180">
         <f t="shared" si="6"/>
         <v>39500</v>
       </c>
-      <c r="R21" s="228">
+      <c r="R21" s="176">
         <f t="shared" si="7"/>
         <v>97029.11</v>
       </c>
-      <c r="S21" s="229">
+      <c r="S21" s="181">
         <f t="shared" si="8"/>
         <v>99940.11</v>
       </c>
@@ -4091,66 +3970,63 @@
         <f t="shared" si="9"/>
         <v>0.10999999999999999</v>
       </c>
-      <c r="V21" s="71" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="217" t="s">
-        <v>90</v>
-      </c>
-      <c r="B22" s="218"/>
-      <c r="C22" s="219" t="s">
+    </row>
+    <row r="22" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="170" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" s="171"/>
+      <c r="C22" s="172" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="220" t="s">
-        <v>150</v>
-      </c>
-      <c r="E22" s="221" t="s">
-        <v>149</v>
-      </c>
-      <c r="F22" s="222">
+      <c r="D22" s="173" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" s="174" t="s">
+        <v>138</v>
+      </c>
+      <c r="F22" s="175">
         <v>7.9</v>
       </c>
-      <c r="G22" s="223">
+      <c r="G22" s="176">
         <v>308030.12</v>
       </c>
-      <c r="H22" s="224"/>
-      <c r="I22" s="224">
+      <c r="H22" s="177"/>
+      <c r="I22" s="177">
         <f>339197.31-I29</f>
         <v>317910.12</v>
       </c>
-      <c r="J22" s="225"/>
-      <c r="K22" s="225">
+      <c r="J22" s="178"/>
+      <c r="K22" s="178">
         <f t="shared" si="10"/>
         <v>-9880</v>
       </c>
-      <c r="L22" s="225"/>
-      <c r="M22" s="226">
+      <c r="L22" s="178"/>
+      <c r="M22" s="179">
         <f t="shared" si="3"/>
         <v>-296.39999999999998</v>
       </c>
-      <c r="N22" s="226">
+      <c r="N22" s="179">
         <f t="shared" si="11"/>
         <v>-10176.4</v>
       </c>
-      <c r="O22" s="225">
+      <c r="O22" s="178">
         <f t="shared" si="4"/>
         <v>54274.941029999994</v>
       </c>
-      <c r="P22" s="227">
+      <c r="P22" s="180">
         <f t="shared" si="5"/>
         <v>13430</v>
       </c>
-      <c r="Q22" s="227">
+      <c r="Q22" s="180">
         <f t="shared" si="6"/>
         <v>39500</v>
       </c>
-      <c r="R22" s="228">
+      <c r="R22" s="176">
         <f t="shared" si="7"/>
         <v>97029.119999999995</v>
       </c>
-      <c r="S22" s="229">
+      <c r="S22" s="181">
         <f t="shared" si="8"/>
         <v>99940.12</v>
       </c>
@@ -4158,62 +4034,59 @@
         <f t="shared" si="9"/>
         <v>0.11999999999999998</v>
       </c>
-      <c r="V22" s="71" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="86"/>
+    </row>
+    <row r="23" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="85"/>
       <c r="B23" s="52"/>
-      <c r="C23" s="219" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" s="230" t="str">
+      <c r="C23" s="172" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="182" t="str">
         <f>D17</f>
         <v>Estevez Norberto Omar</v>
       </c>
-      <c r="E23" s="221" t="s">
-        <v>143</v>
-      </c>
-      <c r="F23" s="222">
+      <c r="E23" s="174" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" s="175">
         <v>0.74</v>
       </c>
-      <c r="G23" s="223">
+      <c r="G23" s="176">
         <v>10596.13</v>
       </c>
-      <c r="H23" s="224"/>
-      <c r="I23" s="224">
+      <c r="H23" s="177"/>
+      <c r="I23" s="177">
         <f>G23</f>
         <v>10596.13</v>
       </c>
-      <c r="J23" s="225"/>
-      <c r="K23" s="225">
+      <c r="J23" s="178"/>
+      <c r="K23" s="178">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L23" s="225"/>
-      <c r="M23" s="226">
+      <c r="L23" s="178"/>
+      <c r="M23" s="179">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N23" s="226">
+      <c r="N23" s="179">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O23" s="225">
+      <c r="O23" s="178">
         <f t="shared" si="4"/>
         <v>5083.9818179999984</v>
       </c>
-      <c r="P23" s="227">
+      <c r="P23" s="180">
         <f t="shared" si="5"/>
         <v>1258</v>
       </c>
-      <c r="Q23" s="225"/>
-      <c r="R23" s="228">
+      <c r="Q23" s="178"/>
+      <c r="R23" s="176">
         <f t="shared" si="7"/>
         <v>6342.13</v>
       </c>
-      <c r="S23" s="229">
+      <c r="S23" s="181">
         <f t="shared" si="8"/>
         <v>6532.13</v>
       </c>
@@ -4221,65 +4094,62 @@
         <f t="shared" si="9"/>
         <v>0.12999999999999998</v>
       </c>
-      <c r="V23" s="71" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="217"/>
-      <c r="B24" s="136"/>
-      <c r="C24" s="219" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="230" t="str">
+    </row>
+    <row r="24" spans="1:22" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="170"/>
+      <c r="B24" s="135"/>
+      <c r="C24" s="172" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="182" t="str">
         <f>D21</f>
         <v>Moro Vanesa Yania / Juan Carlos Moro</v>
       </c>
-      <c r="E24" s="221" t="s">
-        <v>109</v>
-      </c>
-      <c r="F24" s="222">
+      <c r="E24" s="174" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" s="175">
         <v>0.74</v>
       </c>
-      <c r="G24" s="223">
+      <c r="G24" s="176">
         <v>21287.14</v>
       </c>
-      <c r="H24" s="224"/>
-      <c r="I24" s="224">
+      <c r="H24" s="177"/>
+      <c r="I24" s="177">
         <f>G24</f>
         <v>21287.14</v>
       </c>
-      <c r="J24" s="225"/>
-      <c r="K24" s="225">
+      <c r="J24" s="178"/>
+      <c r="K24" s="178">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L24" s="225"/>
-      <c r="M24" s="226">
+      <c r="L24" s="178"/>
+      <c r="M24" s="179">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N24" s="226">
+      <c r="N24" s="179">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O24" s="225">
+      <c r="O24" s="178">
         <f t="shared" si="4"/>
         <v>5083.9818179999984</v>
       </c>
-      <c r="P24" s="227">
+      <c r="P24" s="180">
         <f t="shared" si="5"/>
         <v>1258</v>
       </c>
-      <c r="Q24" s="225">
+      <c r="Q24" s="178">
         <f>'Calculo Servicios  (2)'!H22</f>
         <v>0</v>
       </c>
-      <c r="R24" s="228">
+      <c r="R24" s="176">
         <f t="shared" si="7"/>
         <v>6342.14</v>
       </c>
-      <c r="S24" s="229">
+      <c r="S24" s="181">
         <f t="shared" si="8"/>
         <v>6532.14</v>
       </c>
@@ -4287,115 +4157,115 @@
         <f t="shared" si="9"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="V24" s="71" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="86"/>
+    </row>
+    <row r="25" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="85"/>
       <c r="B25" s="52"/>
-      <c r="C25" s="71" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25" s="88" t="str">
+      <c r="C25" s="283" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="284" t="str">
         <f>D20</f>
         <v>Scarlercio Jorge Omar</v>
       </c>
-      <c r="E25" s="88"/>
-      <c r="F25" s="73">
+      <c r="E25" s="284"/>
+      <c r="F25" s="285">
         <v>0.74</v>
       </c>
-      <c r="G25" s="214">
+      <c r="G25" s="286">
         <v>21287.15</v>
       </c>
-      <c r="H25" s="215"/>
-      <c r="I25" s="211"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46">
+      <c r="H25" s="287"/>
+      <c r="I25" s="287">
+        <f>G25</f>
+        <v>21287.15</v>
+      </c>
+      <c r="J25" s="288"/>
+      <c r="K25" s="288">
         <f t="shared" si="10"/>
-        <v>21287.15</v>
-      </c>
-      <c r="L25" s="46"/>
-      <c r="M25" s="45">
+        <v>0</v>
+      </c>
+      <c r="L25" s="288"/>
+      <c r="M25" s="289">
         <f t="shared" si="3"/>
-        <v>638.61450000000002</v>
-      </c>
-      <c r="N25" s="45">
+        <v>0</v>
+      </c>
+      <c r="N25" s="289">
         <f t="shared" si="11"/>
-        <v>21925.764500000001</v>
-      </c>
-      <c r="O25" s="46">
+        <v>0</v>
+      </c>
+      <c r="O25" s="288">
         <f t="shared" si="4"/>
         <v>5083.9818179999984</v>
       </c>
-      <c r="P25" s="48">
+      <c r="P25" s="290">
         <f t="shared" si="5"/>
         <v>1258</v>
       </c>
-      <c r="Q25" s="46">
+      <c r="Q25" s="288">
         <f>'Calculo Servicios  (2)'!H23</f>
         <v>0</v>
       </c>
-      <c r="R25" s="162">
+      <c r="R25" s="286">
         <f t="shared" si="7"/>
-        <v>28268.15</v>
-      </c>
-      <c r="S25" s="161">
+        <v>6342.15</v>
+      </c>
+      <c r="S25" s="291">
         <f t="shared" si="8"/>
-        <v>29116.15</v>
+        <v>6532.15</v>
       </c>
       <c r="T25" s="31">
         <f t="shared" si="9"/>
         <v>0.15</v>
       </c>
-      <c r="V25" s="71" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="135"/>
-      <c r="B26" s="133"/>
-      <c r="C26" s="72" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" s="141" t="str">
+      <c r="U25" s="292" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="134"/>
+      <c r="B26" s="132"/>
+      <c r="C26" s="71" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="140" t="str">
         <f>D18</f>
         <v>Lopez Gabriela</v>
       </c>
-      <c r="E26" s="138" t="s">
-        <v>144</v>
-      </c>
-      <c r="F26" s="139">
+      <c r="E26" s="137" t="s">
+        <v>133</v>
+      </c>
+      <c r="F26" s="138">
         <v>0.74</v>
       </c>
-      <c r="G26" s="210">
+      <c r="G26" s="161">
         <v>21287.16</v>
       </c>
-      <c r="H26" s="211">
-        <v>0</v>
-      </c>
-      <c r="I26" s="211">
+      <c r="H26" s="164">
+        <v>0</v>
+      </c>
+      <c r="I26" s="164">
         <f>G26</f>
         <v>21287.16</v>
       </c>
-      <c r="J26" s="134" t="e">
+      <c r="J26" s="133" t="e">
         <f>C8*F26/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K26" s="134">
+      <c r="K26" s="133">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L26" s="134"/>
-      <c r="M26" s="140">
+      <c r="L26" s="133"/>
+      <c r="M26" s="139">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N26" s="140">
+      <c r="N26" s="139">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O26" s="134">
+      <c r="O26" s="133">
         <f t="shared" si="4"/>
         <v>5083.9818179999984</v>
       </c>
@@ -4403,15 +4273,15 @@
         <f t="shared" si="5"/>
         <v>1258</v>
       </c>
-      <c r="Q26" s="134">
+      <c r="Q26" s="133">
         <f>'Calculo Servicios  (2)'!H24</f>
         <v>0</v>
       </c>
-      <c r="R26" s="162">
+      <c r="R26" s="161">
         <f t="shared" si="7"/>
         <v>6342.16</v>
       </c>
-      <c r="S26" s="161">
+      <c r="S26" s="160">
         <f t="shared" si="8"/>
         <v>6532.16</v>
       </c>
@@ -4419,31 +4289,28 @@
         <f t="shared" si="9"/>
         <v>0.16</v>
       </c>
-      <c r="V26" s="71" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="86"/>
+    </row>
+    <row r="27" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="85"/>
       <c r="B27" s="52"/>
-      <c r="C27" s="71" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" s="88" t="str">
+      <c r="C27" s="70" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="87" t="str">
         <f>D15</f>
         <v>Cecilia Mariel Cassettari</v>
       </c>
-      <c r="E27" s="88"/>
-      <c r="F27" s="73">
+      <c r="E27" s="87"/>
+      <c r="F27" s="72">
         <v>0.74</v>
       </c>
-      <c r="G27" s="214">
+      <c r="G27" s="167">
         <v>10596.17</v>
       </c>
-      <c r="H27" s="215">
-        <v>0</v>
-      </c>
-      <c r="I27" s="211">
+      <c r="H27" s="168">
+        <v>0</v>
+      </c>
+      <c r="I27" s="164">
         <v>10914.17</v>
       </c>
       <c r="J27" s="46" t="e">
@@ -4475,11 +4342,11 @@
         <f>'Calculo Servicios  (2)'!H25</f>
         <v>0</v>
       </c>
-      <c r="R27" s="162">
+      <c r="R27" s="161">
         <f t="shared" si="7"/>
         <v>6014.17</v>
       </c>
-      <c r="S27" s="161">
+      <c r="S27" s="160">
         <f t="shared" si="8"/>
         <v>6195.17</v>
       </c>
@@ -4487,69 +4354,66 @@
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
-      <c r="V27" s="71" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="156"/>
-      <c r="B28" s="157"/>
-      <c r="C28" s="219" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" s="230" t="str">
+    </row>
+    <row r="28" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="155"/>
+      <c r="B28" s="156"/>
+      <c r="C28" s="172" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="182" t="str">
         <f>D16</f>
         <v>Perez Sebastian</v>
       </c>
-      <c r="E28" s="221" t="s">
-        <v>163</v>
-      </c>
-      <c r="F28" s="231">
+      <c r="E28" s="174" t="s">
+        <v>152</v>
+      </c>
+      <c r="F28" s="183">
         <v>0.74</v>
       </c>
-      <c r="G28" s="223">
+      <c r="G28" s="176">
         <v>10596.18</v>
       </c>
-      <c r="H28" s="223">
-        <v>0</v>
-      </c>
-      <c r="I28" s="224">
+      <c r="H28" s="176">
+        <v>0</v>
+      </c>
+      <c r="I28" s="177">
         <f>G28</f>
         <v>10596.18</v>
       </c>
-      <c r="J28" s="227">
-        <v>0</v>
-      </c>
-      <c r="K28" s="227">
+      <c r="J28" s="180">
+        <v>0</v>
+      </c>
+      <c r="K28" s="180">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L28" s="227"/>
-      <c r="M28" s="232">
+      <c r="L28" s="180"/>
+      <c r="M28" s="184">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N28" s="232">
+      <c r="N28" s="184">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O28" s="227">
+      <c r="O28" s="180">
         <f t="shared" si="4"/>
         <v>5083.9818179999984</v>
       </c>
-      <c r="P28" s="227">
+      <c r="P28" s="180">
         <f t="shared" si="5"/>
         <v>1258</v>
       </c>
-      <c r="Q28" s="227">
+      <c r="Q28" s="180">
         <f>'Calculo Servicios  (2)'!H26</f>
         <v>0</v>
       </c>
-      <c r="R28" s="228">
+      <c r="R28" s="176">
         <f t="shared" si="7"/>
         <v>6342.18</v>
       </c>
-      <c r="S28" s="229">
+      <c r="S28" s="181">
         <f t="shared" si="8"/>
         <v>6532.18</v>
       </c>
@@ -4557,70 +4421,67 @@
         <f t="shared" si="9"/>
         <v>0.18000000000000002</v>
       </c>
-      <c r="V28" s="71" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="135"/>
-      <c r="B29" s="148"/>
-      <c r="C29" s="219" t="s">
-        <v>97</v>
-      </c>
-      <c r="D29" s="230" t="str">
+    </row>
+    <row r="29" spans="1:22" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="134"/>
+      <c r="B29" s="147"/>
+      <c r="C29" s="172" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="182" t="str">
         <f>D22</f>
         <v>Rodriguez Flavio/Rodriguez Mauro</v>
       </c>
-      <c r="E29" s="221" t="s">
-        <v>149</v>
-      </c>
-      <c r="F29" s="233">
+      <c r="E29" s="174" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" s="185">
         <v>0.74</v>
       </c>
-      <c r="G29" s="223">
+      <c r="G29" s="176">
         <v>21287.19</v>
       </c>
-      <c r="H29" s="224">
-        <v>0</v>
-      </c>
-      <c r="I29" s="224">
+      <c r="H29" s="177">
+        <v>0</v>
+      </c>
+      <c r="I29" s="177">
         <f>G29</f>
         <v>21287.19</v>
       </c>
-      <c r="J29" s="225" t="e">
+      <c r="J29" s="178" t="e">
         <f>C8*F29/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="K29" s="225">
+      <c r="K29" s="178">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L29" s="225"/>
-      <c r="M29" s="226">
+      <c r="L29" s="178"/>
+      <c r="M29" s="179">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N29" s="226">
+      <c r="N29" s="179">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O29" s="225">
+      <c r="O29" s="178">
         <f t="shared" si="4"/>
         <v>5083.9818179999984</v>
       </c>
-      <c r="P29" s="227">
+      <c r="P29" s="180">
         <f t="shared" si="5"/>
         <v>1258</v>
       </c>
-      <c r="Q29" s="225">
+      <c r="Q29" s="178">
         <f>'Calculo Servicios  (2)'!H27</f>
         <v>0</v>
       </c>
-      <c r="R29" s="228">
+      <c r="R29" s="176">
         <f t="shared" si="7"/>
         <v>6342.19</v>
       </c>
-      <c r="S29" s="229">
+      <c r="S29" s="181">
         <f t="shared" si="8"/>
         <v>6532.19</v>
       </c>
@@ -4628,11 +4489,8 @@
         <f t="shared" si="9"/>
         <v>0.19000000000000003</v>
       </c>
-      <c r="V29" s="72" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:22" ht="21" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="53"/>
       <c r="B30" s="52"/>
       <c r="C30" s="51"/>
@@ -4656,18 +4514,15 @@
       </c>
       <c r="Q30" s="46"/>
       <c r="R30" s="47"/>
-      <c r="S30" s="85"/>
-      <c r="V30" s="71" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" s="39" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="172"/>
-      <c r="B31" s="173"/>
-      <c r="C31" s="173"/>
+      <c r="S30" s="84"/>
+    </row>
+    <row r="31" spans="1:22" s="39" customFormat="1" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="242"/>
+      <c r="B31" s="243"/>
+      <c r="C31" s="243"/>
       <c r="D31" s="44"/>
       <c r="E31" s="44"/>
-      <c r="F31" s="74"/>
+      <c r="F31" s="73"/>
       <c r="G31" s="42">
         <f>SUM(G11:G30)</f>
         <v>2563556.9000000004</v>
@@ -4678,12 +4533,12 @@
       </c>
       <c r="I31" s="43">
         <f>SUM(I11:I30)</f>
-        <v>2437353.3800000008</v>
+        <v>2458640.5300000007</v>
       </c>
       <c r="J31" s="42"/>
       <c r="K31" s="43">
         <f>SUM(K11:K30)</f>
-        <v>126203.51999999996</v>
+        <v>104916.36999999997</v>
       </c>
       <c r="L31" s="42"/>
       <c r="M31" s="41"/>
@@ -4702,42 +4557,37 @@
       </c>
       <c r="R31" s="43">
         <f>SUM(R11:R29)</f>
-        <v>1456196.8999999997</v>
+        <v>1434270.8999999997</v>
       </c>
       <c r="S31" s="43">
         <f>SUM(S11:S29)</f>
-        <v>1499882.8999999997</v>
-      </c>
-      <c r="V31" s="71" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="169" t="s">
+        <v>1477298.8999999997</v>
+      </c>
+      <c r="V31"/>
+    </row>
+    <row r="32" spans="1:22" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="239" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="170"/>
-      <c r="D32" s="170"/>
-      <c r="E32" s="170"/>
-      <c r="F32" s="170"/>
-      <c r="G32" s="170"/>
-      <c r="H32" s="170"/>
-      <c r="I32" s="170"/>
-      <c r="J32" s="170"/>
-      <c r="K32" s="170"/>
-      <c r="L32" s="170"/>
-      <c r="M32" s="170"/>
-      <c r="N32" s="170"/>
-      <c r="O32" s="170"/>
-      <c r="P32" s="170"/>
-      <c r="Q32" s="170"/>
-      <c r="R32" s="170"/>
-      <c r="S32" s="171"/>
-      <c r="V32" s="71" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C32" s="240"/>
+      <c r="D32" s="240"/>
+      <c r="E32" s="240"/>
+      <c r="F32" s="240"/>
+      <c r="G32" s="240"/>
+      <c r="H32" s="240"/>
+      <c r="I32" s="240"/>
+      <c r="J32" s="240"/>
+      <c r="K32" s="240"/>
+      <c r="L32" s="240"/>
+      <c r="M32" s="240"/>
+      <c r="N32" s="240"/>
+      <c r="O32" s="240"/>
+      <c r="P32" s="240"/>
+      <c r="Q32" s="240"/>
+      <c r="R32" s="240"/>
+      <c r="S32" s="241"/>
+    </row>
+    <row r="33" spans="3:15" x14ac:dyDescent="0.3">
       <c r="F33" s="38"/>
       <c r="G33" s="37"/>
       <c r="H33" s="37"/>
@@ -4747,84 +4597,81 @@
         <v>18</v>
       </c>
       <c r="L33" s="37"/>
-      <c r="V33" s="71" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C34" s="165"/>
-      <c r="D34" s="165"/>
-      <c r="E34" s="165"/>
-      <c r="F34" s="165"/>
-      <c r="G34" s="165"/>
-      <c r="H34" s="165"/>
-      <c r="I34" s="165"/>
-      <c r="J34" s="165"/>
-      <c r="K34" s="165"/>
-      <c r="L34" s="165"/>
-      <c r="M34" s="165"/>
-      <c r="N34" s="165"/>
-      <c r="O34" s="165"/>
-    </row>
-    <row r="35" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C35" s="165"/>
-      <c r="D35" s="165"/>
-      <c r="E35" s="165"/>
-      <c r="F35" s="165"/>
-      <c r="G35" s="165"/>
-      <c r="H35" s="165"/>
-      <c r="I35" s="165"/>
-      <c r="J35" s="165"/>
-      <c r="K35" s="165"/>
-      <c r="L35" s="165"/>
-      <c r="M35" s="165"/>
-      <c r="N35" s="165"/>
-      <c r="O35" s="165"/>
-    </row>
-    <row r="36" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C36" s="165"/>
-      <c r="D36" s="165"/>
-      <c r="E36" s="165"/>
-      <c r="F36" s="165"/>
-      <c r="G36" s="165"/>
-      <c r="H36" s="165"/>
-      <c r="I36" s="165"/>
-      <c r="J36" s="165"/>
-      <c r="K36" s="165"/>
-      <c r="L36" s="165"/>
-      <c r="M36" s="165"/>
-      <c r="N36" s="165"/>
-      <c r="O36" s="165"/>
-    </row>
-    <row r="37" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C37" s="165"/>
-      <c r="D37" s="165"/>
-      <c r="E37" s="165"/>
-      <c r="F37" s="165"/>
-      <c r="G37" s="165"/>
-      <c r="H37" s="165"/>
-      <c r="I37" s="165"/>
-      <c r="J37" s="165"/>
-      <c r="K37" s="165"/>
-      <c r="L37" s="165"/>
-      <c r="M37" s="165"/>
-      <c r="N37" s="165"/>
-      <c r="O37" s="165"/>
-    </row>
-    <row r="38" spans="3:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="165"/>
-      <c r="D38" s="165"/>
-      <c r="E38" s="165"/>
-      <c r="F38" s="165"/>
-      <c r="G38" s="165"/>
-      <c r="H38" s="165"/>
-      <c r="I38" s="165"/>
-      <c r="J38" s="165"/>
-      <c r="K38" s="165"/>
-      <c r="L38" s="165"/>
-      <c r="M38" s="165"/>
-      <c r="N38" s="165"/>
-      <c r="O38" s="165"/>
+    </row>
+    <row r="34" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C34" s="235"/>
+      <c r="D34" s="235"/>
+      <c r="E34" s="235"/>
+      <c r="F34" s="235"/>
+      <c r="G34" s="235"/>
+      <c r="H34" s="235"/>
+      <c r="I34" s="235"/>
+      <c r="J34" s="235"/>
+      <c r="K34" s="235"/>
+      <c r="L34" s="235"/>
+      <c r="M34" s="235"/>
+      <c r="N34" s="235"/>
+      <c r="O34" s="235"/>
+    </row>
+    <row r="35" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C35" s="235"/>
+      <c r="D35" s="235"/>
+      <c r="E35" s="235"/>
+      <c r="F35" s="235"/>
+      <c r="G35" s="235"/>
+      <c r="H35" s="235"/>
+      <c r="I35" s="235"/>
+      <c r="J35" s="235"/>
+      <c r="K35" s="235"/>
+      <c r="L35" s="235"/>
+      <c r="M35" s="235"/>
+      <c r="N35" s="235"/>
+      <c r="O35" s="235"/>
+    </row>
+    <row r="36" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C36" s="235"/>
+      <c r="D36" s="235"/>
+      <c r="E36" s="235"/>
+      <c r="F36" s="235"/>
+      <c r="G36" s="235"/>
+      <c r="H36" s="235"/>
+      <c r="I36" s="235"/>
+      <c r="J36" s="235"/>
+      <c r="K36" s="235"/>
+      <c r="L36" s="235"/>
+      <c r="M36" s="235"/>
+      <c r="N36" s="235"/>
+      <c r="O36" s="235"/>
+    </row>
+    <row r="37" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C37" s="235"/>
+      <c r="D37" s="235"/>
+      <c r="E37" s="235"/>
+      <c r="F37" s="235"/>
+      <c r="G37" s="235"/>
+      <c r="H37" s="235"/>
+      <c r="I37" s="235"/>
+      <c r="J37" s="235"/>
+      <c r="K37" s="235"/>
+      <c r="L37" s="235"/>
+      <c r="M37" s="235"/>
+      <c r="N37" s="235"/>
+      <c r="O37" s="235"/>
+    </row>
+    <row r="38" spans="3:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="235"/>
+      <c r="D38" s="235"/>
+      <c r="E38" s="235"/>
+      <c r="F38" s="235"/>
+      <c r="G38" s="235"/>
+      <c r="H38" s="235"/>
+      <c r="I38" s="235"/>
+      <c r="J38" s="235"/>
+      <c r="K38" s="235"/>
+      <c r="L38" s="235"/>
+      <c r="M38" s="235"/>
+      <c r="N38" s="235"/>
+      <c r="O38" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -4841,1016 +4688,1016 @@
     <mergeCell ref="F6:K9"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="69" fitToWidth="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="64" fitToWidth="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="90" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="90" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" style="90" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="90" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="90" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.42578125" style="90" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" style="90" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.42578125" style="90"/>
-    <col min="13" max="13" width="14.7109375" style="90" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5703125" style="90" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="90"/>
+    <col min="1" max="1" width="12.109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="89" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="89" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.44140625" style="89" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="89" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.44140625" style="89"/>
+    <col min="13" max="13" width="14.6640625" style="89" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5546875" style="89" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.44140625" style="89"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="201" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="202"/>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="203"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="131"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="130" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" s="127"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="129">
+    <row r="1" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="274" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="275"/>
+      <c r="C1" s="275"/>
+      <c r="D1" s="275"/>
+      <c r="E1" s="276"/>
+    </row>
+    <row r="2" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="130"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="129" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="126"/>
+    </row>
+    <row r="3" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="128">
         <f>13+28+19</f>
         <v>60</v>
       </c>
-      <c r="B3" s="84">
+      <c r="B3" s="83">
         <v>10531.71</v>
       </c>
-      <c r="C3" s="128">
+      <c r="C3" s="127">
         <f>+B3/A3</f>
         <v>175.52849999999998</v>
       </c>
-      <c r="D3" s="128">
+      <c r="D3" s="127">
         <v>4863.8999999999996</v>
       </c>
-      <c r="E3" s="127" t="s">
-        <v>138</v>
-      </c>
-      <c r="I3" s="90" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="126"/>
-      <c r="B4" s="125"/>
-      <c r="C4" s="125"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="124"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="123"/>
-      <c r="B5" s="123"/>
-      <c r="C5" s="123"/>
-      <c r="D5" s="123"/>
-      <c r="E5" s="123"/>
-    </row>
-    <row r="6" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="123"/>
-      <c r="B6" s="123"/>
-      <c r="C6" s="123"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="123"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="204" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="205"/>
-      <c r="C7" s="205"/>
-      <c r="D7" s="205"/>
-      <c r="E7" s="205"/>
-      <c r="F7" s="205"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="206"/>
-      <c r="L7" s="90" t="s">
-        <v>70</v>
-      </c>
-      <c r="M7" s="90" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="83">
+      <c r="E3" s="126" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="89" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="125"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="123"/>
+    </row>
+    <row r="5" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="122"/>
+      <c r="B5" s="122"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+    </row>
+    <row r="6" spans="1:15" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="122"/>
+      <c r="B6" s="122"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+    </row>
+    <row r="7" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="277" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="278"/>
+      <c r="C7" s="278"/>
+      <c r="D7" s="278"/>
+      <c r="E7" s="278"/>
+      <c r="F7" s="278"/>
+      <c r="G7" s="278"/>
+      <c r="H7" s="279"/>
+      <c r="L7" s="89" t="s">
+        <v>59</v>
+      </c>
+      <c r="M7" s="89" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="82">
         <v>400523.88</v>
       </c>
-      <c r="B8" s="121" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="121" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="121" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="122">
+      <c r="B8" s="120" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="120" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="120" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="121">
         <f>3935/2</f>
         <v>1967.5</v>
       </c>
-      <c r="F8" s="121" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="121" t="s">
-        <v>69</v>
-      </c>
-      <c r="H8" s="120" t="s">
-        <v>68</v>
-      </c>
-      <c r="K8" s="116">
+      <c r="F8" s="120" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="120" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="119" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" s="115">
         <v>19</v>
       </c>
-      <c r="L8" s="102">
+      <c r="L8" s="101">
         <v>7502.93</v>
       </c>
-      <c r="M8" s="102">
+      <c r="M8" s="101">
         <v>2365.2600000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="119" t="s">
+    <row r="9" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="118" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="116">
+      <c r="B9" s="115">
         <v>1617</v>
       </c>
-      <c r="C9" s="116">
+      <c r="C9" s="115">
         <f>B9+J25</f>
         <v>1689</v>
       </c>
-      <c r="D9" s="116">
+      <c r="D9" s="115">
         <f t="shared" ref="D9:D20" si="0">+C9-B9</f>
         <v>72</v>
       </c>
-      <c r="E9" s="80">
+      <c r="E9" s="79">
         <f>+D9/E8</f>
         <v>3.6594663278271919E-2</v>
       </c>
-      <c r="F9" s="79">
+      <c r="F9" s="78">
         <f>+A8*E9</f>
         <v>14657.036523506989</v>
       </c>
-      <c r="G9" s="79">
+      <c r="G9" s="78">
         <f>+(A8*A23)/12</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H9" s="78">
+      <c r="H9" s="77">
         <f>+G9+F9</f>
         <v>24606.517913595933</v>
       </c>
-      <c r="K9" s="90">
+      <c r="K9" s="89">
         <v>106</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="101">
         <f>+L8*O9</f>
         <v>1575.6152999999999</v>
       </c>
-      <c r="M9" s="90">
+      <c r="M9" s="89">
         <f>M8*21%</f>
         <v>496.70460000000003</v>
       </c>
-      <c r="N9" s="90" t="s">
-        <v>67</v>
-      </c>
-      <c r="O9" s="82">
+      <c r="N9" s="89" t="s">
+        <v>56</v>
+      </c>
+      <c r="O9" s="81">
         <v>0.21</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="117" t="s">
+    <row r="10" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="116">
+      <c r="B10" s="115">
         <v>4104</v>
       </c>
-      <c r="C10" s="116">
+      <c r="C10" s="115">
         <f t="shared" ref="C10:C20" si="1">B10+J26</f>
         <v>4195</v>
       </c>
-      <c r="D10" s="116">
+      <c r="D10" s="115">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="E10" s="80">
+      <c r="E10" s="79">
         <f>+D10/E8</f>
         <v>4.6251588310038116E-2</v>
       </c>
-      <c r="F10" s="79">
+      <c r="F10" s="78">
         <f>+A8*E10</f>
         <v>18524.865606099109</v>
       </c>
-      <c r="G10" s="79">
+      <c r="G10" s="78">
         <f>+G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H10" s="78">
+      <c r="H10" s="77">
         <f>+G10+F10</f>
         <v>28474.346996188055</v>
       </c>
-      <c r="K10" s="90">
+      <c r="K10" s="89">
         <v>60</v>
       </c>
-      <c r="L10" s="102">
+      <c r="L10" s="101">
         <f>+L8*O10</f>
         <v>481.98822320000005</v>
       </c>
-      <c r="M10" s="90">
+      <c r="M10" s="89">
         <f>+M8*6.424%</f>
         <v>151.94430240000003</v>
       </c>
-      <c r="N10" s="90" t="s">
-        <v>66</v>
-      </c>
-      <c r="O10" s="81">
+      <c r="N10" s="89" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="80">
         <v>6.4240000000000005E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="117" t="s">
+    <row r="11" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="116">
+      <c r="B11" s="115">
         <v>7644</v>
       </c>
-      <c r="C11" s="116">
+      <c r="C11" s="115">
         <f t="shared" si="1"/>
         <v>7807</v>
       </c>
-      <c r="D11" s="116">
+      <c r="D11" s="115">
         <f t="shared" si="0"/>
         <v>163</v>
       </c>
-      <c r="E11" s="80">
+      <c r="E11" s="79">
         <f>+D11/E8</f>
         <v>8.2846251588310035E-2</v>
       </c>
-      <c r="F11" s="79">
+      <c r="F11" s="78">
         <f>+A8*E11</f>
         <v>33181.902129606096</v>
       </c>
-      <c r="G11" s="79">
+      <c r="G11" s="78">
         <f>G10</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H11" s="78">
+      <c r="H11" s="77">
         <f>+G11+F11</f>
         <v>43131.383519695039</v>
       </c>
-      <c r="K11" s="90">
+      <c r="K11" s="89">
         <v>79</v>
       </c>
-      <c r="L11" s="102">
+      <c r="L11" s="101">
         <f>+L8*0.001%</f>
         <v>7.5029300000000007E-2</v>
       </c>
-      <c r="M11" s="90">
+      <c r="M11" s="89">
         <v>0.03</v>
       </c>
-      <c r="N11" s="90" t="s">
-        <v>65</v>
-      </c>
-      <c r="O11" s="102">
+      <c r="N11" s="89" t="s">
+        <v>54</v>
+      </c>
+      <c r="O11" s="101">
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="117" t="s">
+    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="116">
+      <c r="B12" s="115">
         <v>6554</v>
       </c>
-      <c r="C12" s="116">
+      <c r="C12" s="115">
         <f t="shared" si="1"/>
         <v>6730</v>
       </c>
-      <c r="D12" s="116">
+      <c r="D12" s="115">
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
-      <c r="E12" s="80">
+      <c r="E12" s="79">
         <f>+D12/E8</f>
         <v>8.9453621346886919E-2</v>
       </c>
-      <c r="F12" s="79">
+      <c r="F12" s="78">
         <f>+A8*E12</f>
         <v>35828.311501905977</v>
       </c>
-      <c r="G12" s="79">
+      <c r="G12" s="78">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H12" s="78">
+      <c r="H12" s="77">
         <f t="shared" ref="H12:H20" si="2">SUM(F12:G12)</f>
         <v>45777.792891994919</v>
       </c>
-      <c r="K12" s="90">
+      <c r="K12" s="89">
         <v>89</v>
       </c>
-      <c r="L12" s="102">
+      <c r="L12" s="101">
         <v>400</v>
       </c>
-      <c r="M12" s="90">
+      <c r="M12" s="89">
         <v>253</v>
       </c>
-      <c r="N12" s="90" t="s">
-        <v>64</v>
-      </c>
-      <c r="O12" s="90">
+      <c r="N12" s="89" t="s">
+        <v>53</v>
+      </c>
+      <c r="O12" s="89">
         <v>653</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="117" t="s">
+    <row r="13" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="116">
+      <c r="B13" s="115">
         <v>7564</v>
       </c>
-      <c r="C13" s="116">
+      <c r="C13" s="115">
         <f t="shared" si="1"/>
         <v>7767</v>
       </c>
-      <c r="D13" s="116">
+      <c r="D13" s="115">
         <f t="shared" si="0"/>
         <v>203</v>
       </c>
-      <c r="E13" s="80">
+      <c r="E13" s="79">
         <f>+D13/E8</f>
         <v>0.10317662007623889</v>
       </c>
-      <c r="F13" s="79">
+      <c r="F13" s="78">
         <f>+A8*E13</f>
         <v>41324.700198221093</v>
       </c>
-      <c r="G13" s="79">
+      <c r="G13" s="78">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H13" s="78">
+      <c r="H13" s="77">
         <f t="shared" si="2"/>
         <v>51274.181588310035</v>
       </c>
-      <c r="K13" s="90">
+      <c r="K13" s="89">
         <v>140</v>
       </c>
-      <c r="L13" s="118">
+      <c r="L13" s="117">
         <f>SUM(L8:L12)-0.45</f>
         <v>9960.1585524999991</v>
       </c>
-      <c r="M13" s="90">
+      <c r="M13" s="89">
         <f>SUM(M8:M12)</f>
         <v>3266.9389024000006</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="117" t="s">
+    <row r="14" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="116">
+      <c r="B14" s="115">
         <v>10119</v>
       </c>
-      <c r="C14" s="116">
+      <c r="C14" s="115">
         <f t="shared" si="1"/>
         <v>10334</v>
       </c>
-      <c r="D14" s="116">
+      <c r="D14" s="115">
         <f t="shared" si="0"/>
         <v>215</v>
       </c>
-      <c r="E14" s="80">
+      <c r="E14" s="79">
         <f>+D14/E8</f>
         <v>0.10927573062261753</v>
       </c>
-      <c r="F14" s="79">
+      <c r="F14" s="78">
         <f>+A8*E14</f>
         <v>43767.539618805589</v>
       </c>
-      <c r="G14" s="79">
+      <c r="G14" s="78">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H14" s="78">
+      <c r="H14" s="77">
         <f t="shared" si="2"/>
         <v>53717.021008894531</v>
       </c>
-      <c r="K14" s="90">
+      <c r="K14" s="89">
         <v>143</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="117" t="s">
+    <row r="15" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="116">
+      <c r="B15" s="115">
         <v>8986</v>
       </c>
-      <c r="C15" s="116">
+      <c r="C15" s="115">
         <f t="shared" si="1"/>
         <v>9068</v>
       </c>
-      <c r="D15" s="116">
+      <c r="D15" s="115">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="E15" s="80">
+      <c r="E15" s="79">
         <f>+D15/E8</f>
         <v>4.1677255400254132E-2</v>
       </c>
-      <c r="F15" s="79">
+      <c r="F15" s="78">
         <f>+A8*E15</f>
         <v>16692.736040660737</v>
       </c>
-      <c r="G15" s="79">
+      <c r="G15" s="78">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H15" s="78">
+      <c r="H15" s="77">
         <f t="shared" si="2"/>
         <v>26642.217430749683</v>
       </c>
-      <c r="K15" s="90">
+      <c r="K15" s="89">
         <v>221</v>
       </c>
-      <c r="L15" s="90">
+      <c r="L15" s="89">
         <f>+L13+M13</f>
         <v>13227.0974549</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="117" t="s">
+    <row r="16" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="116">
+      <c r="B16" s="115">
         <v>7032</v>
       </c>
-      <c r="C16" s="116">
+      <c r="C16" s="115">
         <f t="shared" si="1"/>
         <v>7034</v>
       </c>
-      <c r="D16" s="116">
+      <c r="D16" s="115">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E16" s="80">
+      <c r="E16" s="79">
         <f>+D16/E8</f>
         <v>1.0165184243964421E-3</v>
       </c>
-      <c r="F16" s="79">
+      <c r="F16" s="78">
         <f>+A8*E16</f>
         <v>407.13990343074965</v>
       </c>
-      <c r="G16" s="79">
+      <c r="G16" s="78">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H16" s="78">
+      <c r="H16" s="77">
         <f t="shared" si="2"/>
         <v>10356.621293519693</v>
       </c>
-      <c r="K16" s="90">
+      <c r="K16" s="89">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="117" t="s">
+    <row r="17" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="116">
+      <c r="B17" s="115">
         <v>1623</v>
       </c>
-      <c r="C17" s="116">
+      <c r="C17" s="115">
         <f t="shared" si="1"/>
         <v>1668</v>
       </c>
-      <c r="D17" s="116">
+      <c r="D17" s="115">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="E17" s="80">
+      <c r="E17" s="79">
         <f>+D17/E8</f>
         <v>2.2871664548919948E-2</v>
       </c>
-      <c r="F17" s="79">
+      <c r="F17" s="78">
         <f>+A8*E17</f>
         <v>9160.6478271918677</v>
       </c>
-      <c r="G17" s="79">
+      <c r="G17" s="78">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H17" s="78">
+      <c r="H17" s="77">
         <f t="shared" si="2"/>
         <v>19110.12921728081</v>
       </c>
-      <c r="K17" s="90">
+      <c r="K17" s="89">
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="117" t="s">
+    <row r="18" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="116">
+      <c r="B18" s="115">
         <v>3932</v>
       </c>
-      <c r="C18" s="116">
+      <c r="C18" s="115">
         <f t="shared" si="1"/>
         <v>4021</v>
       </c>
-      <c r="D18" s="116">
+      <c r="D18" s="115">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="E18" s="80">
+      <c r="E18" s="79">
         <f>+D18/E8</f>
         <v>4.5235069885641674E-2</v>
       </c>
-      <c r="F18" s="79">
+      <c r="F18" s="78">
         <f>+A8*E18</f>
         <v>18117.725702668358</v>
       </c>
-      <c r="G18" s="79">
+      <c r="G18" s="78">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H18" s="78">
+      <c r="H18" s="77">
         <f t="shared" si="2"/>
         <v>28067.2070927573</v>
       </c>
-      <c r="K18" s="90">
+      <c r="K18" s="89">
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="117" t="s">
+    <row r="19" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="116">
+      <c r="B19" s="115">
         <v>6887</v>
       </c>
-      <c r="C19" s="116">
+      <c r="C19" s="115">
         <f t="shared" si="1"/>
         <v>6994</v>
       </c>
-      <c r="D19" s="116">
+      <c r="D19" s="115">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="E19" s="80">
+      <c r="E19" s="79">
         <f>+D19/E8</f>
         <v>5.4383735705209657E-2</v>
       </c>
-      <c r="F19" s="79">
+      <c r="F19" s="78">
         <f>+A8*E19</f>
         <v>21781.98483354511</v>
       </c>
-      <c r="G19" s="79">
+      <c r="G19" s="78">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H19" s="78">
+      <c r="H19" s="77">
         <f t="shared" si="2"/>
         <v>31731.466223634052</v>
       </c>
-      <c r="K19" s="90">
+      <c r="K19" s="89">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="117" t="s">
+    <row r="20" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="116">
+      <c r="B20" s="115">
         <v>1884</v>
       </c>
-      <c r="C20" s="116">
+      <c r="C20" s="115">
         <f t="shared" si="1"/>
         <v>2020</v>
       </c>
-      <c r="D20" s="116">
+      <c r="D20" s="115">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="E20" s="80">
+      <c r="E20" s="79">
         <f>+D20/E8</f>
         <v>6.9123252858958067E-2</v>
       </c>
-      <c r="F20" s="79">
+      <c r="F20" s="78">
         <f>+A8*E20</f>
         <v>27685.513433290977</v>
       </c>
-      <c r="G20" s="79">
+      <c r="G20" s="78">
         <f>G9</f>
         <v>9949.481390088944</v>
       </c>
-      <c r="H20" s="78">
+      <c r="H20" s="77">
         <f t="shared" si="2"/>
         <v>37634.994823379922</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="115" t="s">
-        <v>137</v>
-      </c>
-      <c r="B21" s="114"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="113">
+    <row r="21" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="114" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="113"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="112">
         <f>SUM(D9:D20)</f>
         <v>1381</v>
       </c>
-      <c r="E21" s="112"/>
-      <c r="F21" s="92"/>
-      <c r="G21" s="92"/>
-      <c r="H21" s="77">
+      <c r="E21" s="111"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="76">
         <f>SUM(H9:H20)</f>
         <v>400523.88</v>
       </c>
-      <c r="J21" s="102">
+      <c r="J21" s="101">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="76">
+    <row r="22" spans="1:13" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="75">
         <f>+D21/E8</f>
         <v>0.70190597204574334</v>
       </c>
-      <c r="B22" s="111" t="s">
-        <v>63</v>
-      </c>
-      <c r="L22" s="110"/>
-    </row>
-    <row r="23" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="75">
+      <c r="B22" s="110" t="s">
+        <v>52</v>
+      </c>
+      <c r="L22" s="109"/>
+    </row>
+    <row r="23" spans="1:13" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="74">
         <f>100%-A22</f>
         <v>0.29809402795425666</v>
       </c>
-      <c r="B23" s="109" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="108"/>
-      <c r="J25" s="90">
+      <c r="B23" s="108" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="107"/>
+      <c r="J25" s="89">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="J26" s="90">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J26" s="89">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="J27" s="90">
+    <row r="27" spans="1:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J27" s="89">
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B28" s="207" t="s">
-        <v>136</v>
-      </c>
-      <c r="C28" s="208"/>
-      <c r="D28" s="208"/>
-      <c r="E28" s="208"/>
-      <c r="F28" s="209"/>
-      <c r="J28" s="90">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B28" s="280" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="281"/>
+      <c r="D28" s="281"/>
+      <c r="E28" s="281"/>
+      <c r="F28" s="282"/>
+      <c r="J28" s="89">
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B29" s="107" t="s">
-        <v>135</v>
-      </c>
-      <c r="C29" s="106" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="106" t="s">
-        <v>133</v>
-      </c>
-      <c r="E29" s="106" t="s">
-        <v>132</v>
-      </c>
-      <c r="F29" s="105" t="s">
-        <v>131</v>
-      </c>
-      <c r="J29" s="90">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B29" s="106" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29" s="105" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" s="105" t="s">
+        <v>122</v>
+      </c>
+      <c r="E29" s="105" t="s">
+        <v>121</v>
+      </c>
+      <c r="F29" s="104" t="s">
+        <v>120</v>
+      </c>
+      <c r="J29" s="89">
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B30" s="101" t="s">
-        <v>130</v>
-      </c>
-      <c r="C30" s="79">
+    <row r="30" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B30" s="100" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="78">
         <v>4000</v>
       </c>
-      <c r="D30" s="79">
-        <v>0</v>
-      </c>
-      <c r="E30" s="99"/>
-      <c r="F30" s="78">
+      <c r="D30" s="78">
+        <v>0</v>
+      </c>
+      <c r="E30" s="98"/>
+      <c r="F30" s="77">
         <f>+C30</f>
         <v>4000</v>
       </c>
-      <c r="J30" s="104">
+      <c r="J30" s="103">
         <v>215</v>
       </c>
-      <c r="M30" s="90">
+      <c r="M30" s="89">
         <f>+H21-A8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B31" s="101" t="s">
-        <v>129</v>
-      </c>
-      <c r="C31" s="79">
+    <row r="31" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B31" s="100" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="78">
         <v>4000</v>
       </c>
-      <c r="D31" s="79">
-        <v>0</v>
-      </c>
-      <c r="E31" s="99"/>
-      <c r="F31" s="78">
+      <c r="D31" s="78">
+        <v>0</v>
+      </c>
+      <c r="E31" s="98"/>
+      <c r="F31" s="77">
         <f t="shared" ref="F31:F44" si="3">+F30+C31-D31</f>
         <v>8000</v>
       </c>
-      <c r="J31" s="90">
+      <c r="J31" s="89">
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B32" s="101" t="s">
-        <v>128</v>
-      </c>
-      <c r="C32" s="79">
+    <row r="32" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B32" s="100" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" s="78">
         <v>4000</v>
       </c>
-      <c r="D32" s="79">
-        <v>0</v>
-      </c>
-      <c r="E32" s="99"/>
-      <c r="F32" s="78">
+      <c r="D32" s="78">
+        <v>0</v>
+      </c>
+      <c r="E32" s="98"/>
+      <c r="F32" s="77">
         <f t="shared" si="3"/>
         <v>12000</v>
       </c>
-      <c r="J32" s="90">
+      <c r="J32" s="89">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B33" s="101" t="s">
-        <v>127</v>
-      </c>
-      <c r="C33" s="79">
+    <row r="33" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B33" s="100" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="78">
         <v>4000</v>
       </c>
-      <c r="D33" s="79">
-        <v>0</v>
-      </c>
-      <c r="E33" s="99"/>
-      <c r="F33" s="78">
+      <c r="D33" s="78">
+        <v>0</v>
+      </c>
+      <c r="E33" s="98"/>
+      <c r="F33" s="77">
         <f t="shared" si="3"/>
         <v>16000</v>
       </c>
-      <c r="J33" s="90">
+      <c r="J33" s="89">
         <v>45</v>
       </c>
-      <c r="K33" s="103">
+      <c r="K33" s="102">
         <f>11934.02-11933.71</f>
         <v>0.31000000000130967</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B34" s="101" t="s">
-        <v>126</v>
-      </c>
-      <c r="C34" s="79">
+    <row r="34" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B34" s="100" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" s="78">
         <v>4000</v>
       </c>
-      <c r="D34" s="79">
-        <v>0</v>
-      </c>
-      <c r="E34" s="99"/>
-      <c r="F34" s="78">
+      <c r="D34" s="78">
+        <v>0</v>
+      </c>
+      <c r="E34" s="98"/>
+      <c r="F34" s="77">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="J34" s="90">
+      <c r="J34" s="89">
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B35" s="101" t="s">
-        <v>125</v>
-      </c>
-      <c r="C35" s="79">
+    <row r="35" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B35" s="100" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="78">
         <v>4000</v>
       </c>
-      <c r="D35" s="79">
-        <v>0</v>
-      </c>
-      <c r="E35" s="99"/>
-      <c r="F35" s="78">
+      <c r="D35" s="78">
+        <v>0</v>
+      </c>
+      <c r="E35" s="98"/>
+      <c r="F35" s="77">
         <f t="shared" si="3"/>
         <v>24000</v>
       </c>
-      <c r="J35" s="90">
+      <c r="J35" s="89">
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B36" s="101" t="s">
-        <v>124</v>
-      </c>
-      <c r="C36" s="79">
+    <row r="36" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B36" s="100" t="s">
+        <v>113</v>
+      </c>
+      <c r="C36" s="78">
         <v>4000</v>
       </c>
-      <c r="D36" s="79">
-        <v>0</v>
-      </c>
-      <c r="E36" s="99"/>
-      <c r="F36" s="78">
+      <c r="D36" s="78">
+        <v>0</v>
+      </c>
+      <c r="E36" s="98"/>
+      <c r="F36" s="77">
         <f t="shared" si="3"/>
         <v>28000</v>
       </c>
-      <c r="J36" s="90">
+      <c r="J36" s="89">
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B37" s="101" t="s">
-        <v>123</v>
-      </c>
-      <c r="C37" s="100">
+    <row r="37" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B37" s="100" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="99">
         <v>4000</v>
       </c>
-      <c r="D37" s="79">
-        <v>0</v>
-      </c>
-      <c r="E37" s="99"/>
-      <c r="F37" s="78">
+      <c r="D37" s="78">
+        <v>0</v>
+      </c>
+      <c r="E37" s="98"/>
+      <c r="F37" s="77">
         <f t="shared" si="3"/>
         <v>32000</v>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B38" s="101" t="s">
-        <v>122</v>
-      </c>
-      <c r="C38" s="100">
+    <row r="38" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B38" s="100" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="99">
         <v>4000</v>
       </c>
-      <c r="D38" s="100">
+      <c r="D38" s="99">
         <v>3500</v>
       </c>
-      <c r="E38" s="99" t="s">
-        <v>121</v>
-      </c>
-      <c r="F38" s="78">
+      <c r="E38" s="98" t="s">
+        <v>110</v>
+      </c>
+      <c r="F38" s="77">
         <f t="shared" si="3"/>
         <v>32500</v>
       </c>
-      <c r="M38" s="102">
+      <c r="M38" s="101">
         <f>88.05-100</f>
         <v>-11.950000000000003</v>
       </c>
     </row>
-    <row r="39" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B39" s="101" t="s">
-        <v>120</v>
-      </c>
-      <c r="C39" s="100">
+    <row r="39" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B39" s="100" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="99">
         <v>4000</v>
       </c>
-      <c r="D39" s="99"/>
-      <c r="E39" s="99"/>
-      <c r="F39" s="78">
+      <c r="D39" s="98"/>
+      <c r="E39" s="98"/>
+      <c r="F39" s="77">
         <f t="shared" si="3"/>
         <v>36500</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B40" s="101" t="s">
-        <v>119</v>
-      </c>
-      <c r="C40" s="100">
+    <row r="40" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B40" s="100" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="99">
         <v>4000</v>
       </c>
-      <c r="D40" s="99"/>
-      <c r="E40" s="99"/>
-      <c r="F40" s="78">
+      <c r="D40" s="98"/>
+      <c r="E40" s="98"/>
+      <c r="F40" s="77">
         <f t="shared" si="3"/>
         <v>40500</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B41" s="101" t="s">
-        <v>118</v>
-      </c>
-      <c r="C41" s="100">
+    <row r="41" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B41" s="100" t="s">
+        <v>107</v>
+      </c>
+      <c r="C41" s="99">
         <v>4000</v>
       </c>
-      <c r="D41" s="99"/>
-      <c r="E41" s="99"/>
-      <c r="F41" s="78">
+      <c r="D41" s="98"/>
+      <c r="E41" s="98"/>
+      <c r="F41" s="77">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="42" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B42" s="101" t="s">
-        <v>117</v>
-      </c>
-      <c r="C42" s="100">
-        <v>0</v>
-      </c>
-      <c r="D42" s="99"/>
-      <c r="E42" s="99"/>
-      <c r="F42" s="78">
+    <row r="42" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B42" s="100" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" s="99">
+        <v>0</v>
+      </c>
+      <c r="D42" s="98"/>
+      <c r="E42" s="98"/>
+      <c r="F42" s="77">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B43" s="101" t="s">
-        <v>116</v>
-      </c>
-      <c r="C43" s="100">
-        <v>0</v>
-      </c>
-      <c r="D43" s="99"/>
-      <c r="E43" s="99"/>
-      <c r="F43" s="78">
+    <row r="43" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B43" s="100" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" s="99">
+        <v>0</v>
+      </c>
+      <c r="D43" s="98"/>
+      <c r="E43" s="98"/>
+      <c r="F43" s="77">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="44" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B44" s="98" t="s">
-        <v>115</v>
-      </c>
-      <c r="C44" s="97">
-        <v>0</v>
-      </c>
-      <c r="D44" s="96"/>
-      <c r="E44" s="96"/>
-      <c r="F44" s="95">
+    <row r="44" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B44" s="97" t="s">
+        <v>104</v>
+      </c>
+      <c r="C44" s="96">
+        <v>0</v>
+      </c>
+      <c r="D44" s="95"/>
+      <c r="E44" s="95"/>
+      <c r="F44" s="94">
         <f t="shared" si="3"/>
         <v>44500</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B45" s="98" t="s">
-        <v>114</v>
-      </c>
-      <c r="C45" s="97">
-        <v>0</v>
-      </c>
-      <c r="D45" s="96"/>
-      <c r="E45" s="96"/>
-      <c r="F45" s="95">
+    <row r="45" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B45" s="97" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="96">
+        <v>0</v>
+      </c>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
+      <c r="F45" s="94">
         <f>+F43+C45-D45</f>
         <v>44500</v>
       </c>
     </row>
-    <row r="46" spans="2:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="98" t="s">
-        <v>113</v>
-      </c>
-      <c r="C46" s="97">
-        <v>0</v>
-      </c>
-      <c r="D46" s="96"/>
-      <c r="E46" s="96"/>
-      <c r="F46" s="95">
+    <row r="46" spans="2:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B46" s="97" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" s="96">
+        <v>0</v>
+      </c>
+      <c r="D46" s="95"/>
+      <c r="E46" s="95"/>
+      <c r="F46" s="94">
         <f>+F44+C46-D46</f>
         <v>44500</v>
       </c>
     </row>
-    <row r="47" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="94" t="s">
-        <v>112</v>
-      </c>
-      <c r="C47" s="93">
+    <row r="47" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="93" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" s="92">
         <f>-A47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="92"/>
-      <c r="E47" s="92"/>
-      <c r="F47" s="91">
+      <c r="D47" s="91"/>
+      <c r="E47" s="91"/>
+      <c r="F47" s="90">
         <f>+F45+C47-D47</f>
         <v>44500</v>
       </c>
